--- a/Autocoup.xlsx
+++ b/Autocoup.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qingengdu/GitHub/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39268851-95AF-8348-B908-2B4A4869A00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DEF0EB-5C8F-D242-BB61-7BB955D97798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Autocoup!$A$1:$AO$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Reddy!$A$1:$AZ$114</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -4091,10 +4090,10 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
+      <numFmt numFmtId="20" formatCode="dd\-mmm\-yy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
+      <numFmt numFmtId="20" formatCode="dd\-mmm\-yy"/>
     </dxf>
     <dxf>
       <font>
@@ -4572,16 +4571,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4DAD0BB-82E0-7A47-A291-AB504D7E4D73}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AO111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="29.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" style="57" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" style="57" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.33203125" style="9" customWidth="1"/>
     <col min="7" max="7" width="16.5" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.6640625" style="9" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" style="9" bestFit="1" customWidth="1"/>
@@ -4809,7 +4807,7 @@
       <c r="AN2" s="6"/>
       <c r="AO2" s="6"/>
     </row>
-    <row r="3" spans="1:41" s="16" customFormat="1" ht="17" hidden="1">
+    <row r="3" spans="1:41" s="16" customFormat="1" ht="17">
       <c r="A3" s="6">
         <v>703</v>
       </c>
@@ -4912,7 +4910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:41" s="16" customFormat="1" ht="17" hidden="1">
+    <row r="4" spans="1:41" s="16" customFormat="1" ht="17">
       <c r="A4" s="6">
         <v>625</v>
       </c>
@@ -5019,7 +5017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="5" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A5" s="6">
         <v>438</v>
       </c>
@@ -5063,7 +5061,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="6" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="6" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A6" s="6">
         <v>500</v>
       </c>
@@ -5158,7 +5156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="7" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A7" s="6">
         <v>93</v>
       </c>
@@ -5263,7 +5261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="8" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A8" s="6">
         <v>581</v>
       </c>
@@ -5332,7 +5330,7 @@
       <c r="AN8" s="6"/>
       <c r="AO8" s="6"/>
     </row>
-    <row r="9" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="9" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A9" s="6">
         <v>553</v>
       </c>
@@ -5376,7 +5374,7 @@
       <c r="AG9" s="8"/>
       <c r="AH9" s="8"/>
     </row>
-    <row r="10" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="10" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A10" s="21">
         <v>145</v>
       </c>
@@ -5474,7 +5472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="17" hidden="1">
+    <row r="11" spans="1:41" ht="17">
       <c r="A11" s="6">
         <v>616</v>
       </c>
@@ -5571,7 +5569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="17" hidden="1">
+    <row r="12" spans="1:41" ht="17">
       <c r="A12" s="6">
         <v>471</v>
       </c>
@@ -5672,7 +5670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="13" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A13" s="6">
         <v>482</v>
       </c>
@@ -5779,7 +5777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="17" hidden="1">
+    <row r="14" spans="1:41" ht="17">
       <c r="A14" s="6">
         <v>481</v>
       </c>
@@ -5888,7 +5886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:41" ht="17" hidden="1">
+    <row r="15" spans="1:41" ht="17">
       <c r="A15" s="6">
         <v>616</v>
       </c>
@@ -5985,7 +5983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="16" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A16" s="6">
         <v>615</v>
       </c>
@@ -6071,7 +6069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="17" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A17" s="6">
         <v>439</v>
       </c>
@@ -6238,7 +6236,7 @@
       <c r="AN18" s="21"/>
       <c r="AO18" s="21"/>
     </row>
-    <row r="19" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="19" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A19" s="6">
         <v>101</v>
       </c>
@@ -6428,7 +6426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="21" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A21" s="6">
         <v>438</v>
       </c>
@@ -6632,7 +6630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="17" hidden="1">
+    <row r="23" spans="1:41" ht="17">
       <c r="A23" s="21">
         <v>482</v>
       </c>
@@ -6735,7 +6733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="24" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A24" s="6">
         <v>93</v>
       </c>
@@ -6918,7 +6916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="26" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A26" s="6">
         <v>484</v>
       </c>
@@ -7025,7 +7023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:41" ht="17" hidden="1">
+    <row r="27" spans="1:41" ht="17">
       <c r="A27" s="6">
         <v>540</v>
       </c>
@@ -7120,7 +7118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="28" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A28" s="6">
         <v>660</v>
       </c>
@@ -7429,7 +7427,7 @@
       <c r="AN31" s="6"/>
       <c r="AO31" s="6"/>
     </row>
-    <row r="32" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="32" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A32" s="6">
         <v>461</v>
       </c>
@@ -7538,7 +7536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:41" ht="17" hidden="1">
+    <row r="33" spans="1:41" ht="17">
       <c r="A33" s="6">
         <v>41</v>
       </c>
@@ -7720,7 +7718,7 @@
       <c r="AN34" s="6"/>
       <c r="AO34" s="6"/>
     </row>
-    <row r="35" spans="1:41" ht="17" hidden="1">
+    <row r="35" spans="1:41" ht="17">
       <c r="A35" s="6">
         <v>483</v>
       </c>
@@ -7789,7 +7787,7 @@
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
     </row>
-    <row r="36" spans="1:41" ht="17" hidden="1">
+    <row r="36" spans="1:41" ht="17">
       <c r="A36" s="6">
         <v>135</v>
       </c>
@@ -7806,10 +7804,10 @@
         <v>36852</v>
       </c>
       <c r="F36" s="6">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G36" s="6">
-        <v>2000</v>
+        <v>1995</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>1100</v>
@@ -7971,7 +7969,7 @@
       <c r="AN37" s="6"/>
       <c r="AO37" s="6"/>
     </row>
-    <row r="38" spans="1:41" ht="17" hidden="1">
+    <row r="38" spans="1:41" ht="17">
       <c r="A38" s="6">
         <v>437</v>
       </c>
@@ -8074,7 +8072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:41" ht="34" hidden="1">
+    <row r="39" spans="1:41" ht="34">
       <c r="A39" s="21">
         <v>145</v>
       </c>
@@ -8167,7 +8165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:41" ht="17" hidden="1">
+    <row r="40" spans="1:41" ht="17">
       <c r="A40" s="6">
         <v>522</v>
       </c>
@@ -8266,7 +8264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:41" ht="17" hidden="1">
+    <row r="41" spans="1:41" ht="17">
       <c r="A41" s="6">
         <v>373</v>
       </c>
@@ -8371,7 +8369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:41" s="6" customFormat="1" ht="34" hidden="1">
+    <row r="42" spans="1:41" s="6" customFormat="1" ht="34">
       <c r="A42" s="6">
         <v>517</v>
       </c>
@@ -8466,7 +8464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="43" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A43" s="6">
         <v>522</v>
       </c>
@@ -8510,7 +8508,7 @@
       <c r="AG43" s="8"/>
       <c r="AH43" s="8"/>
     </row>
-    <row r="44" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="44" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A44" s="6">
         <v>732</v>
       </c>
@@ -8608,7 +8606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:41" ht="17" hidden="1">
+    <row r="45" spans="1:41" ht="17">
       <c r="A45" s="21">
         <v>150</v>
       </c>
@@ -8701,7 +8699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="46" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A46" s="6">
         <v>811</v>
       </c>
@@ -8781,7 +8779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="47" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A47" s="6">
         <v>483</v>
       </c>
@@ -8876,7 +8874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:41" ht="34" hidden="1">
+    <row r="48" spans="1:41" ht="34">
       <c r="A48" s="6">
         <v>373</v>
       </c>
@@ -8981,7 +8979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:41" ht="17" hidden="1">
+    <row r="49" spans="1:41" ht="17">
       <c r="A49" s="6">
         <v>531</v>
       </c>
@@ -9157,7 +9155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="51" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A51" s="21">
         <v>553</v>
       </c>
@@ -9224,7 +9222,7 @@
       <c r="AN51" s="21"/>
       <c r="AO51" s="21"/>
     </row>
-    <row r="52" spans="1:41" s="6" customFormat="1" ht="34" hidden="1">
+    <row r="52" spans="1:41" s="6" customFormat="1" ht="34">
       <c r="A52" s="6">
         <v>91</v>
       </c>
@@ -9304,7 +9302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="53" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A53" s="6">
         <v>160</v>
       </c>
@@ -9393,7 +9391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="54" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A54" s="6">
         <v>704</v>
       </c>
@@ -9500,7 +9498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:41" ht="17" hidden="1">
+    <row r="55" spans="1:41" ht="17">
       <c r="A55" s="21">
         <v>517</v>
       </c>
@@ -9591,7 +9589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:41" ht="17" hidden="1">
+    <row r="56" spans="1:41" ht="17">
       <c r="A56" s="6">
         <v>434</v>
       </c>
@@ -9694,7 +9692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:41" ht="17" hidden="1">
+    <row r="57" spans="1:41" ht="17">
       <c r="A57" s="6">
         <v>652</v>
       </c>
@@ -9866,7 +9864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:41" ht="17" hidden="1">
+    <row r="59" spans="1:41" ht="17">
       <c r="A59" s="6">
         <v>370</v>
       </c>
@@ -9981,7 +9979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:41" ht="17" hidden="1">
+    <row r="60" spans="1:41" ht="17">
       <c r="A60" s="6">
         <v>411</v>
       </c>
@@ -10084,7 +10082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:41" ht="34" hidden="1">
+    <row r="61" spans="1:41" ht="34">
       <c r="A61" s="21">
         <v>436</v>
       </c>
@@ -10181,7 +10179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:41" ht="34" hidden="1">
+    <row r="62" spans="1:41" ht="34">
       <c r="A62" s="21">
         <v>145</v>
       </c>
@@ -10276,7 +10274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="63" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A63" s="21">
         <v>91</v>
       </c>
@@ -10345,7 +10343,7 @@
       <c r="AN63" s="21"/>
       <c r="AO63" s="21"/>
     </row>
-    <row r="64" spans="1:41" ht="17" hidden="1">
+    <row r="64" spans="1:41" ht="17">
       <c r="A64" s="6">
         <v>840</v>
       </c>
@@ -10456,7 +10454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:41" s="6" customFormat="1" ht="34" hidden="1">
+    <row r="65" spans="1:41" s="6" customFormat="1" ht="34">
       <c r="A65" s="6">
         <v>101</v>
       </c>
@@ -10554,7 +10552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:41" s="6" customFormat="1" ht="34" hidden="1">
+    <row r="66" spans="1:41" s="6" customFormat="1" ht="34">
       <c r="A66" s="6">
         <v>481</v>
       </c>
@@ -10643,7 +10641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="67" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A67" s="21">
         <v>42</v>
       </c>
@@ -10736,7 +10734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:41" ht="17" hidden="1">
+    <row r="68" spans="1:41" ht="17">
       <c r="A68" s="6">
         <v>160</v>
       </c>
@@ -10833,7 +10831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:41" ht="51" hidden="1">
+    <row r="69" spans="1:41" ht="51">
       <c r="A69" s="21">
         <v>345</v>
       </c>
@@ -10936,7 +10934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="70" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A70" s="6">
         <v>490</v>
       </c>
@@ -11031,7 +11029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="71" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A71" s="6">
         <v>145</v>
       </c>
@@ -11117,7 +11115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="72" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A72" s="6">
         <v>552</v>
       </c>
@@ -11206,7 +11204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:41" ht="17" hidden="1">
+    <row r="73" spans="1:41" ht="17">
       <c r="A73" s="6">
         <v>705</v>
       </c>
@@ -11313,7 +11311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:41" ht="17" hidden="1">
+    <row r="74" spans="1:41" ht="17">
       <c r="A74" s="6">
         <v>484</v>
       </c>
@@ -11410,7 +11408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:41" ht="17" hidden="1">
+    <row r="75" spans="1:41" ht="17">
       <c r="A75" s="6">
         <v>701</v>
       </c>
@@ -11515,7 +11513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="76" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A76" s="6">
         <v>452</v>
       </c>
@@ -11754,7 +11752,7 @@
       <c r="AN78" s="21"/>
       <c r="AO78" s="21"/>
     </row>
-    <row r="79" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="79" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A79" s="21">
         <v>165</v>
       </c>
@@ -11851,7 +11849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="80" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A80" s="6">
         <v>517</v>
       </c>
@@ -11931,7 +11929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:41" s="6" customFormat="1" ht="68" hidden="1">
+    <row r="81" spans="1:41" s="6" customFormat="1" ht="68">
       <c r="A81" s="21">
         <v>41</v>
       </c>
@@ -12030,7 +12028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:41" s="6" customFormat="1" ht="34" hidden="1">
+    <row r="82" spans="1:41" s="6" customFormat="1" ht="34">
       <c r="A82" s="21">
         <v>145</v>
       </c>
@@ -12123,7 +12121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:41" ht="34" hidden="1">
+    <row r="83" spans="1:41" ht="34">
       <c r="A83" s="6">
         <v>516</v>
       </c>
@@ -12220,7 +12218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="84" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A84" s="6">
         <v>155</v>
       </c>
@@ -12312,7 +12310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="85" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A85" s="6">
         <v>365</v>
       </c>
@@ -12413,7 +12411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="86" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A86" s="6">
         <v>42</v>
       </c>
@@ -12484,7 +12482,7 @@
       <c r="AN86" s="6"/>
       <c r="AO86" s="6"/>
     </row>
-    <row r="87" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="87" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A87" s="21">
         <v>780</v>
       </c>
@@ -12577,7 +12575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:41" ht="17" hidden="1">
+    <row r="88" spans="1:41" ht="17">
       <c r="A88" s="6">
         <v>702</v>
       </c>
@@ -12684,7 +12682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:41" ht="17" hidden="1">
+    <row r="89" spans="1:41" ht="17">
       <c r="A89" s="6">
         <v>640</v>
       </c>
@@ -12878,7 +12876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="91" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A91" s="6">
         <v>678</v>
       </c>
@@ -12970,7 +12968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:41" ht="17" hidden="1">
+    <row r="92" spans="1:41" ht="17">
       <c r="A92" s="6">
         <v>439</v>
       </c>
@@ -13152,7 +13150,7 @@
       <c r="AG94" s="8"/>
       <c r="AH94" s="8"/>
     </row>
-    <row r="95" spans="1:41" s="16" customFormat="1" ht="17" hidden="1">
+    <row r="95" spans="1:41" s="16" customFormat="1" ht="17">
       <c r="A95" s="6">
         <v>93</v>
       </c>
@@ -13255,7 +13253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:41" ht="17" hidden="1">
+    <row r="96" spans="1:41" ht="17">
       <c r="A96" s="6">
         <v>451</v>
       </c>
@@ -13356,7 +13354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:41" s="21" customFormat="1" ht="34" hidden="1">
+    <row r="97" spans="1:41" s="21" customFormat="1" ht="34">
       <c r="A97" s="6">
         <v>150</v>
       </c>
@@ -13574,7 +13572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="99" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A99" s="6">
         <v>732</v>
       </c>
@@ -13669,7 +13667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:41" ht="17" hidden="1">
+    <row r="100" spans="1:41" ht="17">
       <c r="A100" s="6">
         <v>411</v>
       </c>
@@ -13740,7 +13738,7 @@
       <c r="AN100" s="6"/>
       <c r="AO100" s="6"/>
     </row>
-    <row r="101" spans="1:41" ht="34" hidden="1">
+    <row r="101" spans="1:41" ht="34">
       <c r="A101" s="6">
         <v>345</v>
       </c>
@@ -13835,7 +13833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="102" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A102" s="6">
         <v>95</v>
       </c>
@@ -13938,7 +13936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:41" ht="17" hidden="1">
+    <row r="103" spans="1:41" ht="17">
       <c r="A103" s="6">
         <v>432</v>
       </c>
@@ -14041,7 +14039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:41" s="16" customFormat="1" ht="17" hidden="1">
+    <row r="104" spans="1:41" s="16" customFormat="1" ht="17">
       <c r="A104" s="4">
         <v>2</v>
       </c>
@@ -14232,7 +14230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="107" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A107" s="6">
         <v>404</v>
       </c>
@@ -14333,7 +14331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="108" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A108" s="21">
         <v>433</v>
       </c>
@@ -14416,7 +14414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:41" s="21" customFormat="1" ht="17" hidden="1">
+    <row r="109" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A109" s="6">
         <v>450</v>
       </c>
@@ -14521,7 +14519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:41" s="6" customFormat="1" ht="17" hidden="1">
+    <row r="110" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A110" s="6">
         <v>710</v>
       </c>
@@ -14601,7 +14599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:41" s="21" customFormat="1" ht="71" hidden="1" customHeight="1">
+    <row r="111" spans="1:41" s="21" customFormat="1" ht="71" customHeight="1">
       <c r="A111" s="6">
         <v>500</v>
       </c>
@@ -14710,15 +14708,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO111" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="step down"/>
-        <filter val="Stepped down"/>
-        <filter val="Stepped down and pass power to nephew"/>
-        <filter val="stepped down under pressure"/>
-        <filter val="stepped dwon under pressure"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AO111">
       <sortCondition ref="C1:C111"/>
     </sortState>

--- a/Autocoup.xlsx
+++ b/Autocoup.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qingengdu/GitHub/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DEF0EB-5C8F-D242-BB61-7BB955D97798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E9E882-CC71-2D4C-B522-5C6CB107759A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Data_Source" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Autocoup!$A$1:$AO$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Autocoup!$A$1:$AO$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Reddy!$A$1:$AZ$114</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4256" uniqueCount="1238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4247" uniqueCount="1238">
   <si>
     <t>ccode</t>
   </si>
@@ -4571,7 +4571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4DAD0BB-82E0-7A47-A291-AB504D7E4D73}">
-  <dimension ref="A1:AO111"/>
+  <dimension ref="A1:AO110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.33203125" style="9" bestFit="1" customWidth="1"/>
@@ -10274,276 +10274,296 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:41" s="6" customFormat="1" ht="17">
-      <c r="A63" s="21">
-        <v>91</v>
-      </c>
-      <c r="B63" s="21" t="s">
-        <v>745</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>767</v>
-      </c>
-      <c r="D63" s="54">
-        <v>38744</v>
-      </c>
-      <c r="E63" s="54">
-        <v>39992</v>
-      </c>
-      <c r="F63" s="21">
-        <v>2009</v>
-      </c>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I63" s="31" t="s">
+    <row r="63" spans="1:41" ht="17">
+      <c r="A63" s="6">
+        <v>840</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="D63" s="55">
+        <v>24106</v>
+      </c>
+      <c r="E63" s="55">
+        <v>31468</v>
+      </c>
+      <c r="F63" s="6">
+        <v>1972</v>
+      </c>
+      <c r="G63" s="6">
+        <v>1976</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I63" s="6" t="s">
         <v>1023</v>
       </c>
-      <c r="J63" s="22" t="s">
+      <c r="J63" s="7" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="M63" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="N63" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="O63" s="6">
+        <v>1977</v>
+      </c>
+      <c r="P63" s="6">
+        <v>1972</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>1976</v>
+      </c>
+      <c r="R63" s="6">
+        <v>1972</v>
+      </c>
+      <c r="S63" s="6">
+        <v>1969</v>
+      </c>
+      <c r="T63" s="6">
+        <v>1972</v>
+      </c>
+      <c r="U63" s="6"/>
+      <c r="V63" s="6"/>
+      <c r="W63" s="6">
+        <v>1972</v>
+      </c>
+      <c r="X63" s="6">
+        <v>1972</v>
+      </c>
+      <c r="Y63" s="6"/>
+      <c r="Z63" s="6">
+        <v>1972</v>
+      </c>
+      <c r="AA63" s="6"/>
+      <c r="AB63" s="6"/>
+      <c r="AC63" s="6"/>
+      <c r="AD63" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="AE63" s="6"/>
+      <c r="AF63" s="6">
+        <v>608</v>
+      </c>
+      <c r="AG63" s="8">
+        <v>24106</v>
+      </c>
+      <c r="AH63" s="8">
+        <v>31468</v>
+      </c>
+      <c r="AI63" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ63" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AK63" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="AL63" s="6">
+        <v>20.14227</v>
+      </c>
+      <c r="AM63" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN63" s="6">
+        <v>9</v>
+      </c>
+      <c r="AO63" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:41" s="6" customFormat="1" ht="34">
+      <c r="A64" s="6">
+        <v>101</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D64" s="55">
+        <v>18580</v>
+      </c>
+      <c r="E64" s="55">
+        <v>21208</v>
+      </c>
+      <c r="F64" s="6">
+        <v>1953</v>
+      </c>
+      <c r="G64" s="6">
+        <v>1957</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J64" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="K63" s="22" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L63" s="22" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M63" s="22" t="s">
-        <v>1200</v>
-      </c>
-      <c r="N63" s="22" t="s">
-        <v>1008</v>
-      </c>
-      <c r="O63" s="21"/>
-      <c r="P63" s="21"/>
-      <c r="Q63" s="21"/>
-      <c r="R63" s="21"/>
-      <c r="S63" s="21"/>
-      <c r="T63" s="21"/>
-      <c r="U63" s="21"/>
-      <c r="V63" s="21"/>
-      <c r="W63" s="21"/>
-      <c r="X63" s="21"/>
-      <c r="Y63" s="21"/>
-      <c r="Z63" s="21"/>
-      <c r="AA63" s="21"/>
-      <c r="AB63" s="21"/>
-      <c r="AC63" s="21"/>
-      <c r="AD63" s="21"/>
-      <c r="AE63" s="21"/>
-      <c r="AF63" s="21"/>
-      <c r="AG63" s="21"/>
-      <c r="AH63" s="21"/>
-      <c r="AI63" s="21"/>
-      <c r="AJ63" s="21"/>
-      <c r="AK63" s="21"/>
-      <c r="AL63" s="21"/>
-      <c r="AM63" s="21"/>
-      <c r="AN63" s="21"/>
-      <c r="AO63" s="21"/>
-    </row>
-    <row r="64" spans="1:41" ht="17">
-      <c r="A64" s="6">
-        <v>840</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D64" s="55">
-        <v>24106</v>
-      </c>
-      <c r="E64" s="55">
-        <v>31468</v>
-      </c>
-      <c r="F64" s="6">
-        <v>1972</v>
-      </c>
-      <c r="G64" s="6">
-        <v>1976</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>1228</v>
       </c>
       <c r="K64" s="7" t="s">
         <v>1024</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="M64" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N64" s="7" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="O64" s="6">
-        <v>1977</v>
+        <v>1957</v>
       </c>
       <c r="P64" s="6">
-        <v>1972</v>
-      </c>
-      <c r="Q64" s="6">
-        <v>1976</v>
-      </c>
-      <c r="R64" s="6">
-        <v>1972</v>
-      </c>
-      <c r="S64" s="6">
-        <v>1969</v>
-      </c>
-      <c r="T64" s="6">
-        <v>1972</v>
-      </c>
-      <c r="U64" s="6"/>
-      <c r="V64" s="6"/>
-      <c r="W64" s="6">
-        <v>1972</v>
+        <v>1957</v>
+      </c>
+      <c r="U64" s="6">
+        <v>1952</v>
       </c>
       <c r="X64" s="6">
-        <v>1972</v>
-      </c>
-      <c r="Y64" s="6"/>
+        <v>1950</v>
+      </c>
+      <c r="Y64" s="6">
+        <v>1958</v>
+      </c>
       <c r="Z64" s="6">
-        <v>1972</v>
-      </c>
-      <c r="AA64" s="6"/>
-      <c r="AB64" s="6"/>
-      <c r="AC64" s="6"/>
+        <v>1952</v>
+      </c>
+      <c r="AA64" s="6">
+        <v>1950</v>
+      </c>
       <c r="AD64" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="AE64" s="6"/>
+        <v>52</v>
+      </c>
       <c r="AF64" s="6">
-        <v>608</v>
+        <v>862</v>
       </c>
       <c r="AG64" s="8">
-        <v>24106</v>
+        <v>18580</v>
       </c>
       <c r="AH64" s="8">
-        <v>31468</v>
+        <v>21208</v>
       </c>
       <c r="AI64" s="6">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="AJ64" s="6" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="AK64" s="6" t="s">
-        <v>336</v>
+        <v>127</v>
       </c>
       <c r="AL64" s="6">
-        <v>20.14227</v>
+        <v>7.19015</v>
       </c>
       <c r="AM64" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN64" s="6">
         <v>4</v>
       </c>
-      <c r="AN64" s="6">
-        <v>9</v>
-      </c>
       <c r="AO64" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:41" s="6" customFormat="1" ht="34">
       <c r="A65" s="6">
-        <v>101</v>
+        <v>481</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>123</v>
+        <v>234</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>124</v>
+        <v>235</v>
       </c>
       <c r="D65" s="55">
-        <v>18580</v>
+        <v>22145</v>
       </c>
       <c r="E65" s="55">
-        <v>21208</v>
+        <v>24804</v>
       </c>
       <c r="F65" s="6">
-        <v>1953</v>
+        <v>1961</v>
       </c>
       <c r="G65" s="6">
-        <v>1957</v>
+        <v>1967</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>138</v>
+        <v>944</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L65" s="7" t="s">
-        <v>1195</v>
+        <v>1023</v>
+      </c>
+      <c r="L65" s="36" t="s">
+        <v>1202</v>
       </c>
       <c r="M65" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N65" s="7" t="s">
-        <v>1207</v>
-      </c>
-      <c r="O65" s="6">
-        <v>1957</v>
+        <v>1205</v>
       </c>
       <c r="P65" s="6">
-        <v>1957</v>
-      </c>
-      <c r="U65" s="6">
-        <v>1952</v>
+        <v>1961</v>
       </c>
       <c r="X65" s="6">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="Y65" s="6">
-        <v>1958</v>
+        <v>1967</v>
       </c>
       <c r="Z65" s="6">
-        <v>1952</v>
-      </c>
-      <c r="AA65" s="6">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="AD65" s="6" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AF65" s="6">
-        <v>862</v>
+        <v>266</v>
       </c>
       <c r="AG65" s="8">
-        <v>18580</v>
+        <v>20961</v>
       </c>
       <c r="AH65" s="8">
-        <v>21208</v>
+        <v>24804</v>
       </c>
       <c r="AI65" s="6">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="AJ65" s="6" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="AK65" s="6" t="s">
-        <v>127</v>
+        <v>236</v>
       </c>
       <c r="AL65" s="6">
-        <v>7.19015</v>
+        <v>10.51436</v>
       </c>
       <c r="AM65" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN65" s="6">
         <v>4</v>
@@ -10552,472 +10572,469 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:41" s="6" customFormat="1" ht="34">
-      <c r="A66" s="6">
-        <v>481</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="D66" s="55">
-        <v>22145</v>
-      </c>
-      <c r="E66" s="55">
-        <v>24804</v>
-      </c>
-      <c r="F66" s="6">
-        <v>1961</v>
-      </c>
-      <c r="G66" s="6">
+    <row r="66" spans="1:41" s="6" customFormat="1" ht="17">
+      <c r="A66" s="21">
+        <v>42</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>672</v>
+      </c>
+      <c r="D66" s="54">
+        <v>36755</v>
+      </c>
+      <c r="E66" s="54">
+        <v>38215</v>
+      </c>
+      <c r="F66" s="21">
+        <v>2002</v>
+      </c>
+      <c r="G66" s="21"/>
+      <c r="H66" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I66" s="31" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J66" s="22" t="s">
+        <v>765</v>
+      </c>
+      <c r="K66" s="22" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L66" s="35" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M66" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="N66" s="22" t="s">
+        <v>1205</v>
+      </c>
+      <c r="O66" s="21"/>
+      <c r="P66" s="21">
+        <v>2002</v>
+      </c>
+      <c r="Q66" s="21"/>
+      <c r="R66" s="21"/>
+      <c r="S66" s="21"/>
+      <c r="T66" s="21"/>
+      <c r="U66" s="21"/>
+      <c r="V66" s="21"/>
+      <c r="W66" s="21"/>
+      <c r="X66" s="21"/>
+      <c r="Y66" s="21"/>
+      <c r="Z66" s="21"/>
+      <c r="AA66" s="21"/>
+      <c r="AB66" s="21"/>
+      <c r="AC66" s="21"/>
+      <c r="AD66" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE66" s="21"/>
+      <c r="AF66" s="21">
+        <v>214</v>
+      </c>
+      <c r="AG66" s="24">
+        <v>36755</v>
+      </c>
+      <c r="AH66" s="24">
+        <v>38215</v>
+      </c>
+      <c r="AI66" s="21">
+        <v>8</v>
+      </c>
+      <c r="AJ66" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK66" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="AL66" s="21">
+        <v>3.9945279999999999</v>
+      </c>
+      <c r="AM66" s="21">
+        <v>2</v>
+      </c>
+      <c r="AN66" s="21">
+        <v>1</v>
+      </c>
+      <c r="AO66" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:41" ht="17">
+      <c r="A67" s="6">
+        <v>160</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="D67" s="55">
+        <v>32697</v>
+      </c>
+      <c r="E67" s="55">
+        <v>36504</v>
+      </c>
+      <c r="F67" s="6">
+        <v>1993</v>
+      </c>
+      <c r="G67" s="6">
+        <v>1993</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>956</v>
+      </c>
+      <c r="K67" s="42" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M67" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="N67" s="7" t="s">
+        <v>1214</v>
+      </c>
+      <c r="O67" s="6">
+        <v>1995</v>
+      </c>
+      <c r="P67" s="6">
+        <v>1993</v>
+      </c>
+      <c r="Q67" s="6"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="6"/>
+      <c r="T67" s="6"/>
+      <c r="U67" s="6"/>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6"/>
+      <c r="X67" s="6"/>
+      <c r="Y67" s="6"/>
+      <c r="Z67" s="6"/>
+      <c r="AA67" s="6"/>
+      <c r="AB67" s="6"/>
+      <c r="AC67" s="6"/>
+      <c r="AD67" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE67" s="6"/>
+      <c r="AF67" s="6">
+        <v>32</v>
+      </c>
+      <c r="AG67" s="8">
+        <v>32332</v>
+      </c>
+      <c r="AH67" s="8">
+        <v>36504</v>
+      </c>
+      <c r="AI67" s="6">
+        <v>8</v>
+      </c>
+      <c r="AJ67" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK67" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="AL67" s="6">
+        <v>11.4145</v>
+      </c>
+      <c r="AM67" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN67" s="6">
+        <v>2</v>
+      </c>
+      <c r="AO67" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:41" ht="51">
+      <c r="A68" s="21">
+        <v>345</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="C68" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="D68" s="54">
+        <v>32643</v>
+      </c>
+      <c r="E68" s="54">
+        <v>36806</v>
+      </c>
+      <c r="F68" s="21">
+        <v>1990</v>
+      </c>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I68" s="31" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J68" s="22" t="s">
+        <v>549</v>
+      </c>
+      <c r="K68" s="22" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L68" s="22" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M68" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="N68" s="22" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O68" s="21">
+        <v>2000</v>
+      </c>
+      <c r="P68" s="21">
+        <v>1997</v>
+      </c>
+      <c r="Q68" s="21">
+        <v>2000</v>
+      </c>
+      <c r="R68" s="21"/>
+      <c r="S68" s="21"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="21"/>
+      <c r="V68" s="21">
+        <v>1991</v>
+      </c>
+      <c r="W68" s="21"/>
+      <c r="X68" s="21">
+        <v>1991</v>
+      </c>
+      <c r="Y68" s="21"/>
+      <c r="Z68" s="21">
+        <v>1991</v>
+      </c>
+      <c r="AA68" s="21"/>
+      <c r="AB68" s="21"/>
+      <c r="AC68" s="21"/>
+      <c r="AD68" s="21" t="s">
+        <v>550</v>
+      </c>
+      <c r="AE68" s="21"/>
+      <c r="AF68" s="21">
+        <v>890</v>
+      </c>
+      <c r="AG68" s="24">
+        <v>32643</v>
+      </c>
+      <c r="AH68" s="24">
+        <v>36806</v>
+      </c>
+      <c r="AI68" s="21">
+        <v>-5</v>
+      </c>
+      <c r="AJ68" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="AK68" s="21" t="s">
+        <v>551</v>
+      </c>
+      <c r="AL68" s="21">
+        <v>11.38988</v>
+      </c>
+      <c r="AM68" s="21">
+        <v>1</v>
+      </c>
+      <c r="AN68" s="21">
+        <v>5</v>
+      </c>
+      <c r="AO68" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:41" s="6" customFormat="1" ht="17">
+      <c r="A69" s="6">
+        <v>490</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D69" s="55">
+        <v>24071</v>
+      </c>
+      <c r="E69" s="55">
+        <v>35566</v>
+      </c>
+      <c r="F69" s="6">
         <v>1967</v>
       </c>
-      <c r="H66" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>944</v>
-      </c>
-      <c r="K66" s="7" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L66" s="36" t="s">
+      <c r="G69" s="6">
+        <v>1970</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L69" s="36" t="s">
         <v>1202</v>
       </c>
-      <c r="M66" s="7" t="s">
+      <c r="M69" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="N66" s="7" t="s">
+      <c r="N69" s="7" t="s">
         <v>1205</v>
       </c>
-      <c r="P66" s="6">
-        <v>1961</v>
-      </c>
-      <c r="X66" s="6">
-        <v>1960</v>
-      </c>
-      <c r="Y66" s="6">
+      <c r="O69" s="6">
+        <v>1984</v>
+      </c>
+      <c r="P69" s="6">
         <v>1967</v>
       </c>
-      <c r="Z66" s="6">
-        <v>1960</v>
-      </c>
-      <c r="AD66" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF66" s="6">
-        <v>266</v>
-      </c>
-      <c r="AG66" s="8">
-        <v>20961</v>
-      </c>
-      <c r="AH66" s="8">
-        <v>24804</v>
-      </c>
-      <c r="AI66" s="6">
-        <v>-7</v>
-      </c>
-      <c r="AJ66" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK66" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="AL66" s="6">
-        <v>10.51436</v>
-      </c>
-      <c r="AM66" s="6">
+      <c r="X69" s="6">
+        <v>1965</v>
+      </c>
+      <c r="Y69" s="6">
+        <v>1997</v>
+      </c>
+      <c r="Z69" s="6">
+        <v>1970</v>
+      </c>
+      <c r="AA69" s="6">
+        <v>1965</v>
+      </c>
+      <c r="AD69" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF69" s="6">
+        <v>180</v>
+      </c>
+      <c r="AG69" s="8">
+        <v>24071</v>
+      </c>
+      <c r="AH69" s="8">
+        <v>35566</v>
+      </c>
+      <c r="AI69" s="6">
+        <v>-9</v>
+      </c>
+      <c r="AJ69" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK69" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="AL69" s="6">
+        <v>31.45007</v>
+      </c>
+      <c r="AM69" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN69" s="6">
         <v>3</v>
       </c>
-      <c r="AN66" s="6">
-        <v>4</v>
-      </c>
-      <c r="AO66" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:41" s="6" customFormat="1" ht="17">
-      <c r="A67" s="21">
-        <v>42</v>
-      </c>
-      <c r="B67" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="C67" s="27" t="s">
-        <v>672</v>
-      </c>
-      <c r="D67" s="54">
-        <v>36755</v>
-      </c>
-      <c r="E67" s="54">
-        <v>38215</v>
-      </c>
-      <c r="F67" s="21">
-        <v>2002</v>
-      </c>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I67" s="31" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J67" s="22" t="s">
-        <v>765</v>
-      </c>
-      <c r="K67" s="22" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L67" s="35" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M67" s="22" t="s">
-        <v>1200</v>
-      </c>
-      <c r="N67" s="22" t="s">
-        <v>1205</v>
-      </c>
-      <c r="O67" s="21"/>
-      <c r="P67" s="21">
-        <v>2002</v>
-      </c>
-      <c r="Q67" s="21"/>
-      <c r="R67" s="21"/>
-      <c r="S67" s="21"/>
-      <c r="T67" s="21"/>
-      <c r="U67" s="21"/>
-      <c r="V67" s="21"/>
-      <c r="W67" s="21"/>
-      <c r="X67" s="21"/>
-      <c r="Y67" s="21"/>
-      <c r="Z67" s="21"/>
-      <c r="AA67" s="21"/>
-      <c r="AB67" s="21"/>
-      <c r="AC67" s="21"/>
-      <c r="AD67" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE67" s="21"/>
-      <c r="AF67" s="21">
-        <v>214</v>
-      </c>
-      <c r="AG67" s="24">
-        <v>36755</v>
-      </c>
-      <c r="AH67" s="24">
-        <v>38215</v>
-      </c>
-      <c r="AI67" s="21">
-        <v>8</v>
-      </c>
-      <c r="AJ67" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK67" s="21" t="s">
-        <v>673</v>
-      </c>
-      <c r="AL67" s="21">
-        <v>3.9945279999999999</v>
-      </c>
-      <c r="AM67" s="21">
-        <v>2</v>
-      </c>
-      <c r="AN67" s="21">
-        <v>1</v>
-      </c>
-      <c r="AO67" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:41" ht="17">
-      <c r="A68" s="6">
-        <v>160</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>578</v>
-      </c>
-      <c r="D68" s="55">
-        <v>32697</v>
-      </c>
-      <c r="E68" s="55">
-        <v>36504</v>
-      </c>
-      <c r="F68" s="6">
-        <v>1993</v>
-      </c>
-      <c r="G68" s="6">
-        <v>1993</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I68" s="6" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>956</v>
-      </c>
-      <c r="K68" s="42" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L68" s="7" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M68" s="7" t="s">
-        <v>1201</v>
-      </c>
-      <c r="N68" s="7" t="s">
-        <v>1214</v>
-      </c>
-      <c r="O68" s="6">
-        <v>1995</v>
-      </c>
-      <c r="P68" s="6">
-        <v>1993</v>
-      </c>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
-      <c r="V68" s="6"/>
-      <c r="W68" s="6"/>
-      <c r="X68" s="6"/>
-      <c r="Y68" s="6"/>
-      <c r="Z68" s="6"/>
-      <c r="AA68" s="6"/>
-      <c r="AB68" s="6"/>
-      <c r="AC68" s="6"/>
-      <c r="AD68" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE68" s="6"/>
-      <c r="AF68" s="6">
-        <v>32</v>
-      </c>
-      <c r="AG68" s="8">
-        <v>32332</v>
-      </c>
-      <c r="AH68" s="8">
-        <v>36504</v>
-      </c>
-      <c r="AI68" s="6">
-        <v>8</v>
-      </c>
-      <c r="AJ68" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK68" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="AL68" s="6">
-        <v>11.4145</v>
-      </c>
-      <c r="AM68" s="6">
-        <v>5</v>
-      </c>
-      <c r="AN68" s="6">
-        <v>2</v>
-      </c>
-      <c r="AO68" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:41" ht="51">
-      <c r="A69" s="21">
-        <v>345</v>
-      </c>
-      <c r="B69" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="C69" s="27" t="s">
-        <v>548</v>
-      </c>
-      <c r="D69" s="54">
-        <v>32643</v>
-      </c>
-      <c r="E69" s="54">
-        <v>36806</v>
-      </c>
-      <c r="F69" s="21">
-        <v>1990</v>
-      </c>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I69" s="31" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J69" s="22" t="s">
-        <v>549</v>
-      </c>
-      <c r="K69" s="22" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L69" s="22" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M69" s="22" t="s">
-        <v>1200</v>
-      </c>
-      <c r="N69" s="22" t="s">
-        <v>1209</v>
-      </c>
-      <c r="O69" s="21">
-        <v>2000</v>
-      </c>
-      <c r="P69" s="21">
-        <v>1997</v>
-      </c>
-      <c r="Q69" s="21">
-        <v>2000</v>
-      </c>
-      <c r="R69" s="21"/>
-      <c r="S69" s="21"/>
-      <c r="T69" s="21"/>
-      <c r="U69" s="21"/>
-      <c r="V69" s="21">
-        <v>1991</v>
-      </c>
-      <c r="W69" s="21"/>
-      <c r="X69" s="21">
-        <v>1991</v>
-      </c>
-      <c r="Y69" s="21"/>
-      <c r="Z69" s="21">
-        <v>1991</v>
-      </c>
-      <c r="AA69" s="21"/>
-      <c r="AB69" s="21"/>
-      <c r="AC69" s="21"/>
-      <c r="AD69" s="21" t="s">
-        <v>550</v>
-      </c>
-      <c r="AE69" s="21"/>
-      <c r="AF69" s="21">
-        <v>890</v>
-      </c>
-      <c r="AG69" s="24">
-        <v>32643</v>
-      </c>
-      <c r="AH69" s="24">
-        <v>36806</v>
-      </c>
-      <c r="AI69" s="21">
-        <v>-5</v>
-      </c>
-      <c r="AJ69" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK69" s="21" t="s">
-        <v>551</v>
-      </c>
-      <c r="AL69" s="21">
-        <v>11.38988</v>
-      </c>
-      <c r="AM69" s="21">
-        <v>1</v>
-      </c>
-      <c r="AN69" s="21">
-        <v>5</v>
-      </c>
-      <c r="AO69" s="21">
+      <c r="AO69" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A70" s="6">
-        <v>490</v>
+        <v>145</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>294</v>
+        <v>43</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>295</v>
+        <v>708</v>
       </c>
       <c r="D70" s="55">
-        <v>24071</v>
+        <v>38739</v>
       </c>
       <c r="E70" s="55">
-        <v>35566</v>
+        <v>43779</v>
       </c>
       <c r="F70" s="6">
-        <v>1967</v>
+        <v>2013</v>
       </c>
       <c r="G70" s="6">
-        <v>1970</v>
+        <v>2017</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>45</v>
+        <v>1100</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>296</v>
+        <v>1226</v>
       </c>
       <c r="K70" s="7" t="s">
         <v>1024</v>
       </c>
-      <c r="L70" s="36" t="s">
-        <v>1202</v>
+      <c r="L70" s="7" t="s">
+        <v>1194</v>
       </c>
       <c r="M70" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="O70" s="6">
-        <v>1984</v>
+        <v>2009</v>
       </c>
       <c r="P70" s="6">
-        <v>1967</v>
-      </c>
-      <c r="X70" s="6">
-        <v>1965</v>
-      </c>
-      <c r="Y70" s="6">
-        <v>1997</v>
-      </c>
-      <c r="Z70" s="6">
-        <v>1970</v>
-      </c>
-      <c r="AA70" s="6">
-        <v>1965</v>
+        <v>2008</v>
+      </c>
+      <c r="W70" s="6">
+        <v>2017</v>
       </c>
       <c r="AD70" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF70" s="6">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="AG70" s="8">
-        <v>24071</v>
+        <v>38739</v>
       </c>
       <c r="AH70" s="8">
-        <v>35566</v>
+        <v>43779</v>
       </c>
       <c r="AI70" s="6">
-        <v>-9</v>
+        <v>8</v>
       </c>
       <c r="AJ70" s="6" t="s">
         <v>48</v>
       </c>
       <c r="AK70" s="6" t="s">
-        <v>297</v>
+        <v>709</v>
       </c>
       <c r="AL70" s="6">
-        <v>31.45007</v>
+        <v>13.78933</v>
       </c>
       <c r="AM70" s="6">
         <v>2</v>
@@ -11026,30 +11043,30 @@
         <v>3</v>
       </c>
       <c r="AO70" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A71" s="6">
-        <v>145</v>
+        <v>552</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>708</v>
+        <v>478</v>
+      </c>
+      <c r="C71" s="45" t="s">
+        <v>479</v>
       </c>
       <c r="D71" s="55">
-        <v>38739</v>
+        <v>29284</v>
       </c>
       <c r="E71" s="55">
-        <v>43779</v>
+        <v>43060</v>
       </c>
       <c r="F71" s="6">
-        <v>2013</v>
+        <v>1987</v>
       </c>
       <c r="G71" s="6">
-        <v>2017</v>
+        <v>1987</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>1100</v>
@@ -11058,144 +11075,165 @@
         <v>1023</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>1226</v>
+        <v>45</v>
       </c>
       <c r="K71" s="7" t="s">
         <v>1024</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>1194</v>
+        <v>1223</v>
       </c>
       <c r="M71" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N71" s="7" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="O71" s="6">
-        <v>2009</v>
-      </c>
-      <c r="P71" s="6">
         <v>2008</v>
       </c>
+      <c r="S71" s="6">
+        <v>1987</v>
+      </c>
+      <c r="V71" s="6">
+        <v>2001</v>
+      </c>
       <c r="W71" s="6">
-        <v>2017</v>
+        <v>1983</v>
       </c>
       <c r="AD71" s="6" t="s">
-        <v>47</v>
+        <v>387</v>
       </c>
       <c r="AF71" s="6">
-        <v>68</v>
+        <v>716</v>
       </c>
       <c r="AG71" s="8">
-        <v>38739</v>
+        <v>29284</v>
       </c>
       <c r="AH71" s="8">
-        <v>43779</v>
+        <v>43060</v>
       </c>
       <c r="AI71" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AJ71" s="6" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="AK71" s="6" t="s">
-        <v>709</v>
+        <v>480</v>
       </c>
       <c r="AL71" s="6">
-        <v>13.78933</v>
+        <v>37.690829999999998</v>
       </c>
       <c r="AM71" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN71" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO71" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:41" s="6" customFormat="1" ht="17">
+    <row r="72" spans="1:41" ht="17">
       <c r="A72" s="6">
-        <v>552</v>
+        <v>705</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="C72" s="45" t="s">
-        <v>479</v>
+        <v>557</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>558</v>
       </c>
       <c r="D72" s="55">
-        <v>29284</v>
+        <v>32987</v>
       </c>
       <c r="E72" s="55">
-        <v>43060</v>
+        <v>43544</v>
       </c>
       <c r="F72" s="6">
-        <v>1987</v>
+        <v>1998</v>
       </c>
       <c r="G72" s="6">
-        <v>1987</v>
+        <v>2007</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>1100</v>
+        <v>213</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>1023</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>45</v>
+        <v>1226</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>1223</v>
+        <v>1193</v>
       </c>
       <c r="M72" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N72" s="7" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="O72" s="6">
-        <v>2008</v>
-      </c>
-      <c r="S72" s="6">
-        <v>1987</v>
-      </c>
+        <v>1999</v>
+      </c>
+      <c r="P72" s="6">
+        <v>1995</v>
+      </c>
+      <c r="Q72" s="6">
+        <v>1998</v>
+      </c>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
       <c r="V72" s="6">
-        <v>2001</v>
-      </c>
-      <c r="W72" s="6">
-        <v>1983</v>
-      </c>
+        <v>1994</v>
+      </c>
+      <c r="W72" s="6"/>
+      <c r="X72" s="6">
+        <v>1991</v>
+      </c>
+      <c r="Y72" s="6">
+        <v>2019</v>
+      </c>
+      <c r="Z72" s="6">
+        <v>1995</v>
+      </c>
+      <c r="AA72" s="6"/>
+      <c r="AB72" s="6"/>
+      <c r="AC72" s="6"/>
       <c r="AD72" s="6" t="s">
-        <v>387</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AE72" s="6"/>
       <c r="AF72" s="6">
-        <v>716</v>
+        <v>398</v>
       </c>
       <c r="AG72" s="8">
-        <v>29284</v>
+        <v>32987</v>
       </c>
       <c r="AH72" s="8">
-        <v>43060</v>
+        <v>43544</v>
       </c>
       <c r="AI72" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ72" s="6" t="s">
-        <v>154</v>
+        <v>60</v>
       </c>
       <c r="AK72" s="6" t="s">
-        <v>480</v>
+        <v>559</v>
       </c>
       <c r="AL72" s="6">
-        <v>37.690829999999998</v>
+        <v>28.88372</v>
       </c>
       <c r="AM72" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN72" s="6">
         <v>5</v>
@@ -11206,241 +11244,239 @@
     </row>
     <row r="73" spans="1:41" ht="17">
       <c r="A73" s="6">
-        <v>705</v>
+        <v>484</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>557</v>
+        <v>201</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>558</v>
+        <v>316</v>
       </c>
       <c r="D73" s="55">
-        <v>32987</v>
+        <v>25204</v>
       </c>
       <c r="E73" s="55">
-        <v>43544</v>
+        <v>28202</v>
       </c>
       <c r="F73" s="6">
-        <v>1998</v>
+        <v>1969</v>
       </c>
       <c r="G73" s="6">
-        <v>2007</v>
+        <v>1970</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>213</v>
+        <v>665</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>1023</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>1226</v>
+        <v>57</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>1193</v>
+        <v>1222</v>
       </c>
       <c r="M73" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N73" s="7" t="s">
-        <v>1210</v>
-      </c>
-      <c r="O73" s="6">
-        <v>1999</v>
-      </c>
+        <v>1205</v>
+      </c>
+      <c r="O73" s="6"/>
       <c r="P73" s="6">
-        <v>1995</v>
-      </c>
-      <c r="Q73" s="6">
-        <v>1998</v>
-      </c>
+        <v>1970</v>
+      </c>
+      <c r="Q73" s="6"/>
       <c r="R73" s="6"/>
       <c r="S73" s="6"/>
       <c r="T73" s="6"/>
       <c r="U73" s="6"/>
-      <c r="V73" s="6">
-        <v>1994</v>
-      </c>
-      <c r="W73" s="6"/>
-      <c r="X73" s="6">
-        <v>1991</v>
-      </c>
-      <c r="Y73" s="6">
-        <v>2019</v>
-      </c>
-      <c r="Z73" s="6">
-        <v>1995</v>
-      </c>
+      <c r="V73" s="6"/>
+      <c r="W73" s="6">
+        <v>1969</v>
+      </c>
+      <c r="X73" s="6"/>
+      <c r="Y73" s="6"/>
+      <c r="Z73" s="6"/>
       <c r="AA73" s="6"/>
       <c r="AB73" s="6"/>
       <c r="AC73" s="6"/>
       <c r="AD73" s="6" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="AE73" s="6"/>
       <c r="AF73" s="6">
-        <v>398</v>
+        <v>178</v>
       </c>
       <c r="AG73" s="8">
-        <v>32987</v>
+        <v>25204</v>
       </c>
       <c r="AH73" s="8">
-        <v>43544</v>
+        <v>28202</v>
       </c>
       <c r="AI73" s="6">
+        <v>-7</v>
+      </c>
+      <c r="AJ73" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK73" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="AL73" s="6">
+        <v>8.2024620000000006</v>
+      </c>
+      <c r="AM73" s="6">
         <v>0</v>
       </c>
-      <c r="AJ73" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AK73" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="AL73" s="6">
-        <v>28.88372</v>
-      </c>
-      <c r="AM73" s="6">
-        <v>1</v>
-      </c>
       <c r="AN73" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO73" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:41" ht="17">
       <c r="A74" s="6">
-        <v>484</v>
+        <v>701</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>201</v>
+        <v>560</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>316</v>
+        <v>561</v>
       </c>
       <c r="D74" s="55">
-        <v>25204</v>
+        <v>33173</v>
       </c>
       <c r="E74" s="55">
-        <v>28202</v>
+        <v>39072</v>
       </c>
       <c r="F74" s="6">
-        <v>1969</v>
+        <v>1999</v>
       </c>
       <c r="G74" s="6">
-        <v>1970</v>
+        <v>1999</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>665</v>
+        <v>213</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>1023</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>1222</v>
+        <v>1199</v>
       </c>
       <c r="M74" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N74" s="7" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="O74" s="6"/>
       <c r="P74" s="6">
-        <v>1970</v>
-      </c>
-      <c r="Q74" s="6"/>
+        <v>1994</v>
+      </c>
+      <c r="Q74" s="6">
+        <v>1999</v>
+      </c>
       <c r="R74" s="6"/>
       <c r="S74" s="6"/>
       <c r="T74" s="6"/>
       <c r="U74" s="6"/>
-      <c r="V74" s="6"/>
-      <c r="W74" s="6">
-        <v>1969</v>
-      </c>
-      <c r="X74" s="6"/>
-      <c r="Y74" s="6"/>
-      <c r="Z74" s="6"/>
+      <c r="V74" s="6">
+        <v>1992</v>
+      </c>
+      <c r="W74" s="6"/>
+      <c r="X74" s="6">
+        <v>1991</v>
+      </c>
+      <c r="Y74" s="6">
+        <v>2006</v>
+      </c>
+      <c r="Z74" s="6">
+        <v>1990</v>
+      </c>
       <c r="AA74" s="6"/>
       <c r="AB74" s="6"/>
       <c r="AC74" s="6"/>
       <c r="AD74" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AE74" s="6"/>
       <c r="AF74" s="6">
-        <v>178</v>
+        <v>795</v>
       </c>
       <c r="AG74" s="8">
-        <v>25204</v>
+        <v>33173</v>
       </c>
       <c r="AH74" s="8">
-        <v>28202</v>
+        <v>39072</v>
       </c>
       <c r="AI74" s="6">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="AJ74" s="6" t="s">
         <v>48</v>
       </c>
       <c r="AK74" s="6" t="s">
-        <v>319</v>
+        <v>563</v>
       </c>
       <c r="AL74" s="6">
-        <v>8.2024620000000006</v>
+        <v>16.139530000000001</v>
       </c>
       <c r="AM74" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN74" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO74" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:41" ht="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A75" s="6">
-        <v>701</v>
+        <v>452</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>560</v>
+        <v>179</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>561</v>
+        <v>180</v>
       </c>
       <c r="D75" s="55">
-        <v>33173</v>
+        <v>19074</v>
       </c>
       <c r="E75" s="55">
-        <v>39072</v>
+        <v>24162</v>
       </c>
       <c r="F75" s="6">
-        <v>1999</v>
+        <v>1964</v>
       </c>
       <c r="G75" s="6">
-        <v>1999</v>
+        <v>1964</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>213</v>
+        <v>1234</v>
       </c>
       <c r="I75" s="6" t="s">
         <v>1023</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="L75" s="7" t="s">
         <v>1199</v>
@@ -11449,270 +11485,232 @@
         <v>1201</v>
       </c>
       <c r="N75" s="7" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O75" s="6"/>
+        <v>1210</v>
+      </c>
       <c r="P75" s="6">
-        <v>1994</v>
-      </c>
-      <c r="Q75" s="6">
-        <v>1999</v>
-      </c>
-      <c r="R75" s="6"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6">
-        <v>1992</v>
-      </c>
-      <c r="W75" s="6"/>
+        <v>1964</v>
+      </c>
+      <c r="T75" s="6">
+        <v>1958</v>
+      </c>
       <c r="X75" s="6">
-        <v>1991</v>
-      </c>
-      <c r="Y75" s="6">
-        <v>2006</v>
+        <v>1960</v>
       </c>
       <c r="Z75" s="6">
-        <v>1990</v>
-      </c>
-      <c r="AA75" s="6"/>
-      <c r="AB75" s="6"/>
-      <c r="AC75" s="6"/>
+        <v>1960</v>
+      </c>
       <c r="AD75" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE75" s="6"/>
+        <v>181</v>
+      </c>
       <c r="AF75" s="6">
-        <v>795</v>
+        <v>288</v>
       </c>
       <c r="AG75" s="8">
-        <v>33173</v>
+        <v>19074</v>
       </c>
       <c r="AH75" s="8">
-        <v>39072</v>
+        <v>24162</v>
       </c>
       <c r="AI75" s="6">
+        <v>-8</v>
+      </c>
+      <c r="AJ75" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="AK75" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>13.92066</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN75" s="6">
+        <v>4</v>
+      </c>
+      <c r="AO75" s="6">
         <v>0</v>
-      </c>
-      <c r="AJ75" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK75" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="AL75" s="6">
-        <v>16.139530000000001</v>
-      </c>
-      <c r="AM75" s="6">
-        <v>2</v>
-      </c>
-      <c r="AN75" s="6">
-        <v>3</v>
-      </c>
-      <c r="AO75" s="6">
-        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A76" s="6">
-        <v>452</v>
+        <v>565</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>179</v>
+        <v>647</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>180</v>
+        <v>648</v>
       </c>
       <c r="D76" s="55">
-        <v>19074</v>
+        <v>32953</v>
       </c>
       <c r="E76" s="55">
-        <v>24162</v>
+        <v>38432</v>
       </c>
       <c r="F76" s="6">
-        <v>1964</v>
+        <v>1998</v>
       </c>
       <c r="G76" s="6">
-        <v>1964</v>
+        <v>1998</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>1234</v>
+        <v>213</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>1023</v>
       </c>
-      <c r="J76" s="7" t="s">
-        <v>138</v>
+      <c r="J76" s="36" t="s">
+        <v>1230</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="M76" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N76" s="7" t="s">
-        <v>1210</v>
+        <v>1206</v>
+      </c>
+      <c r="O76" s="6">
+        <v>2004</v>
       </c>
       <c r="P76" s="6">
-        <v>1964</v>
-      </c>
-      <c r="T76" s="6">
-        <v>1958</v>
-      </c>
-      <c r="X76" s="6">
-        <v>1960</v>
-      </c>
-      <c r="Z76" s="6">
-        <v>1960</v>
+        <v>1998</v>
       </c>
       <c r="AD76" s="6" t="s">
-        <v>181</v>
+        <v>47</v>
       </c>
       <c r="AF76" s="6">
-        <v>288</v>
+        <v>516</v>
       </c>
       <c r="AG76" s="8">
-        <v>19074</v>
+        <v>32953</v>
       </c>
       <c r="AH76" s="8">
-        <v>24162</v>
+        <v>38432</v>
       </c>
       <c r="AI76" s="6">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="AJ76" s="6" t="s">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="AK76" s="6" t="s">
-        <v>182</v>
+        <v>650</v>
       </c>
       <c r="AL76" s="6">
-        <v>13.92066</v>
+        <v>14.99042</v>
       </c>
       <c r="AM76" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN76" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO76" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:41" s="6" customFormat="1" ht="17">
-      <c r="A77" s="6">
-        <v>565</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>648</v>
-      </c>
-      <c r="D77" s="55">
-        <v>32953</v>
-      </c>
-      <c r="E77" s="55">
-        <v>38432</v>
-      </c>
-      <c r="F77" s="6">
-        <v>1998</v>
-      </c>
-      <c r="G77" s="6">
-        <v>1998</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="I77" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:41" ht="17">
+      <c r="A77" s="21">
+        <v>475</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="C77" s="52" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D77" s="54">
+        <v>36309</v>
+      </c>
+      <c r="E77" s="54">
+        <v>39231</v>
+      </c>
+      <c r="F77" s="21">
+        <v>2006</v>
+      </c>
+      <c r="G77" s="21"/>
+      <c r="H77" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I77" s="21" t="s">
         <v>1023</v>
       </c>
-      <c r="J77" s="36" t="s">
+      <c r="J77" s="22" t="s">
         <v>1230</v>
       </c>
-      <c r="K77" s="7" t="s">
+      <c r="K77" s="22" t="s">
         <v>1023</v>
       </c>
-      <c r="L77" s="7" t="s">
+      <c r="L77" s="22" t="s">
         <v>1194</v>
       </c>
-      <c r="M77" s="7" t="s">
-        <v>1201</v>
-      </c>
-      <c r="N77" s="7" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O77" s="6">
-        <v>2004</v>
-      </c>
-      <c r="P77" s="6">
-        <v>1998</v>
-      </c>
-      <c r="AD77" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF77" s="6">
-        <v>516</v>
-      </c>
-      <c r="AG77" s="8">
-        <v>32953</v>
-      </c>
-      <c r="AH77" s="8">
-        <v>38432</v>
-      </c>
-      <c r="AI77" s="6">
-        <v>6</v>
-      </c>
-      <c r="AJ77" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK77" s="6" t="s">
-        <v>650</v>
-      </c>
-      <c r="AL77" s="6">
-        <v>14.99042</v>
-      </c>
-      <c r="AM77" s="6">
-        <v>8</v>
-      </c>
-      <c r="AN77" s="6">
-        <v>2</v>
-      </c>
-      <c r="AO77" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:41" ht="17">
+      <c r="M77" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="N77" s="22"/>
+      <c r="O77" s="21"/>
+      <c r="P77" s="21"/>
+      <c r="Q77" s="21"/>
+      <c r="R77" s="21"/>
+      <c r="S77" s="21"/>
+      <c r="T77" s="21"/>
+      <c r="U77" s="21"/>
+      <c r="V77" s="21"/>
+      <c r="W77" s="21"/>
+      <c r="X77" s="21"/>
+      <c r="Y77" s="21"/>
+      <c r="Z77" s="21"/>
+      <c r="AA77" s="21"/>
+      <c r="AB77" s="21"/>
+      <c r="AC77" s="21"/>
+      <c r="AD77" s="21"/>
+      <c r="AE77" s="21"/>
+      <c r="AF77" s="21"/>
+      <c r="AG77" s="24"/>
+      <c r="AH77" s="24"/>
+      <c r="AI77" s="21"/>
+      <c r="AJ77" s="21"/>
+      <c r="AK77" s="21"/>
+      <c r="AL77" s="21"/>
+      <c r="AM77" s="21"/>
+      <c r="AN77" s="21"/>
+      <c r="AO77" s="21"/>
+    </row>
+    <row r="78" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A78" s="21">
-        <v>475</v>
+        <v>165</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>592</v>
-      </c>
-      <c r="C78" s="52" t="s">
-        <v>1145</v>
+        <v>375</v>
+      </c>
+      <c r="C78" s="44" t="s">
+        <v>376</v>
       </c>
       <c r="D78" s="54">
-        <v>36309</v>
+        <v>24812</v>
       </c>
       <c r="E78" s="54">
-        <v>39231</v>
+        <v>26359</v>
       </c>
       <c r="F78" s="21">
-        <v>2006</v>
+        <v>1971</v>
       </c>
       <c r="G78" s="21"/>
       <c r="H78" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I78" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="I78" s="31" t="s">
         <v>1023</v>
       </c>
       <c r="J78" s="22" t="s">
-        <v>1230</v>
+        <v>765</v>
       </c>
       <c r="K78" s="22" t="s">
         <v>1023</v>
@@ -11723,13 +11721,19 @@
       <c r="M78" s="22" t="s">
         <v>1200</v>
       </c>
-      <c r="N78" s="22"/>
+      <c r="N78" s="22" t="s">
+        <v>953</v>
+      </c>
       <c r="O78" s="21"/>
       <c r="P78" s="21"/>
       <c r="Q78" s="21"/>
       <c r="R78" s="21"/>
-      <c r="S78" s="21"/>
-      <c r="T78" s="21"/>
+      <c r="S78" s="21">
+        <v>1971</v>
+      </c>
+      <c r="T78" s="21">
+        <v>1972</v>
+      </c>
       <c r="U78" s="21"/>
       <c r="V78" s="21"/>
       <c r="W78" s="21"/>
@@ -11739,214 +11743,240 @@
       <c r="AA78" s="21"/>
       <c r="AB78" s="21"/>
       <c r="AC78" s="21"/>
-      <c r="AD78" s="21"/>
-      <c r="AE78" s="21"/>
-      <c r="AF78" s="21"/>
-      <c r="AG78" s="24"/>
-      <c r="AH78" s="24"/>
-      <c r="AI78" s="21"/>
-      <c r="AJ78" s="21"/>
-      <c r="AK78" s="21"/>
-      <c r="AL78" s="21"/>
-      <c r="AM78" s="21"/>
-      <c r="AN78" s="21"/>
-      <c r="AO78" s="21"/>
+      <c r="AD78" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE78" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="AF78" s="21">
+        <v>858</v>
+      </c>
+      <c r="AG78" s="24">
+        <v>24812</v>
+      </c>
+      <c r="AH78" s="24">
+        <v>26359</v>
+      </c>
+      <c r="AI78" s="21">
+        <v>8</v>
+      </c>
+      <c r="AJ78" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="AK78" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL78" s="21">
+        <v>4.232558</v>
+      </c>
+      <c r="AM78" s="21">
+        <v>4</v>
+      </c>
+      <c r="AN78" s="21">
+        <v>2</v>
+      </c>
+      <c r="AO78" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:41" s="6" customFormat="1" ht="17">
-      <c r="A79" s="21">
-        <v>165</v>
-      </c>
-      <c r="B79" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="C79" s="44" t="s">
-        <v>376</v>
-      </c>
-      <c r="D79" s="54">
-        <v>24812</v>
-      </c>
-      <c r="E79" s="54">
-        <v>26359</v>
-      </c>
-      <c r="F79" s="21">
-        <v>1971</v>
-      </c>
-      <c r="G79" s="21"/>
-      <c r="H79" s="21" t="s">
-        <v>426</v>
-      </c>
-      <c r="I79" s="31" t="s">
+      <c r="A79" s="6">
+        <v>517</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="D79" s="55">
+        <v>34534</v>
+      </c>
+      <c r="E79" s="55">
+        <v>42735</v>
+      </c>
+      <c r="F79" s="6">
+        <v>2003</v>
+      </c>
+      <c r="G79" s="6">
+        <v>2003</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="K79" s="7" t="s">
         <v>1023</v>
       </c>
-      <c r="J79" s="22" t="s">
-        <v>765</v>
-      </c>
-      <c r="K79" s="22" t="s">
+      <c r="L79" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M79" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="N79" s="7" t="s">
+        <v>1005</v>
+      </c>
+      <c r="P79" s="6">
+        <v>2003</v>
+      </c>
+      <c r="AD79" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF79" s="6">
+        <v>646</v>
+      </c>
+      <c r="AG79" s="8">
+        <v>34534</v>
+      </c>
+      <c r="AH79" s="8">
+        <v>42735</v>
+      </c>
+      <c r="AI79" s="6">
+        <v>-6</v>
+      </c>
+      <c r="AJ79" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK79" s="6" t="s">
+        <v>690</v>
+      </c>
+      <c r="AL79" s="6">
+        <v>22.437760000000001</v>
+      </c>
+      <c r="AM79" s="6">
+        <v>9</v>
+      </c>
+      <c r="AN79" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO79" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:41" s="6" customFormat="1" ht="68">
+      <c r="A80" s="21">
+        <v>41</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C80" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="D80" s="54">
+        <v>18393</v>
+      </c>
+      <c r="E80" s="54">
+        <v>20801</v>
+      </c>
+      <c r="F80" s="21">
+        <v>1950</v>
+      </c>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I80" s="21" t="s">
         <v>1023</v>
       </c>
-      <c r="L79" s="22" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M79" s="22" t="s">
+      <c r="J80" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="K80" s="22" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L80" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M80" s="22" t="s">
         <v>1200</v>
       </c>
-      <c r="N79" s="22" t="s">
-        <v>953</v>
-      </c>
-      <c r="O79" s="21"/>
-      <c r="P79" s="21"/>
-      <c r="Q79" s="21"/>
-      <c r="R79" s="21"/>
-      <c r="S79" s="21">
-        <v>1971</v>
-      </c>
-      <c r="T79" s="21">
-        <v>1972</v>
-      </c>
-      <c r="U79" s="21"/>
-      <c r="V79" s="21"/>
-      <c r="W79" s="21"/>
-      <c r="X79" s="21"/>
-      <c r="Y79" s="21"/>
-      <c r="Z79" s="21"/>
-      <c r="AA79" s="21"/>
-      <c r="AB79" s="21"/>
-      <c r="AC79" s="21"/>
-      <c r="AD79" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE79" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="AF79" s="21">
-        <v>858</v>
-      </c>
-      <c r="AG79" s="24">
-        <v>24812</v>
-      </c>
-      <c r="AH79" s="24">
-        <v>26359</v>
-      </c>
-      <c r="AI79" s="21">
-        <v>8</v>
-      </c>
-      <c r="AJ79" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK79" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL79" s="21">
-        <v>4.232558</v>
-      </c>
-      <c r="AM79" s="21">
-        <v>4</v>
-      </c>
-      <c r="AN79" s="21">
-        <v>2</v>
-      </c>
-      <c r="AO79" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:41" s="6" customFormat="1" ht="17">
-      <c r="A80" s="6">
-        <v>517</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>688</v>
-      </c>
-      <c r="D80" s="55">
-        <v>34534</v>
-      </c>
-      <c r="E80" s="55">
-        <v>42735</v>
-      </c>
-      <c r="F80" s="6">
-        <v>2003</v>
-      </c>
-      <c r="G80" s="6">
-        <v>2003</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I80" s="6" t="s">
-        <v>1024</v>
-      </c>
-      <c r="J80" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="K80" s="7" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L80" s="7" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M80" s="7" t="s">
-        <v>1201</v>
-      </c>
-      <c r="N80" s="7" t="s">
-        <v>1005</v>
-      </c>
-      <c r="P80" s="6">
-        <v>2003</v>
-      </c>
-      <c r="AD80" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF80" s="6">
-        <v>646</v>
-      </c>
-      <c r="AG80" s="8">
-        <v>34534</v>
-      </c>
-      <c r="AH80" s="8">
-        <v>42735</v>
-      </c>
-      <c r="AI80" s="6">
-        <v>-6</v>
-      </c>
-      <c r="AJ80" s="6" t="s">
+      <c r="N80" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="O80" s="21"/>
+      <c r="P80" s="21"/>
+      <c r="Q80" s="21"/>
+      <c r="R80" s="21"/>
+      <c r="S80" s="21"/>
+      <c r="T80" s="21"/>
+      <c r="U80" s="21"/>
+      <c r="V80" s="21"/>
+      <c r="W80" s="21"/>
+      <c r="X80" s="21">
+        <v>1950</v>
+      </c>
+      <c r="Y80" s="21">
+        <v>1956</v>
+      </c>
+      <c r="Z80" s="21">
+        <v>1950</v>
+      </c>
+      <c r="AA80" s="21">
+        <v>1950</v>
+      </c>
+      <c r="AB80" s="21"/>
+      <c r="AC80" s="21"/>
+      <c r="AD80" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE80" s="21"/>
+      <c r="AF80" s="21">
+        <v>332</v>
+      </c>
+      <c r="AG80" s="24">
+        <v>18393</v>
+      </c>
+      <c r="AH80" s="24">
+        <v>20801</v>
+      </c>
+      <c r="AI80" s="21">
+        <v>-5</v>
+      </c>
+      <c r="AJ80" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="AK80" s="6" t="s">
-        <v>690</v>
-      </c>
-      <c r="AL80" s="6">
-        <v>22.437760000000001</v>
-      </c>
-      <c r="AM80" s="6">
-        <v>9</v>
-      </c>
-      <c r="AN80" s="6">
-        <v>1</v>
-      </c>
-      <c r="AO80" s="6">
+      <c r="AK80" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="AL80" s="21">
+        <v>6.5882350000000001</v>
+      </c>
+      <c r="AM80" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:41" s="6" customFormat="1" ht="68">
+      <c r="AN80" s="21">
+        <v>1</v>
+      </c>
+      <c r="AO80" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:41" s="6" customFormat="1" ht="34">
       <c r="A81" s="21">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C81" s="44" t="s">
-        <v>96</v>
+        <v>43</v>
+      </c>
+      <c r="C81" s="27" t="s">
+        <v>274</v>
       </c>
       <c r="D81" s="54">
-        <v>18393</v>
+        <v>22134</v>
       </c>
       <c r="E81" s="54">
-        <v>20801</v>
+        <v>23685</v>
       </c>
       <c r="F81" s="21">
-        <v>1950</v>
+        <v>1964</v>
       </c>
       <c r="G81" s="21"/>
       <c r="H81" s="21" t="s">
@@ -11956,22 +11986,24 @@
         <v>1023</v>
       </c>
       <c r="J81" s="22" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="K81" s="22" t="s">
         <v>1024</v>
       </c>
       <c r="L81" s="22" t="s">
-        <v>1223</v>
+        <v>1194</v>
       </c>
       <c r="M81" s="22" t="s">
         <v>1200</v>
       </c>
-      <c r="N81" s="58" t="s">
-        <v>99</v>
+      <c r="N81" s="22" t="s">
+        <v>1221</v>
       </c>
       <c r="O81" s="21"/>
-      <c r="P81" s="21"/>
+      <c r="P81" s="21">
+        <v>1964</v>
+      </c>
       <c r="Q81" s="21"/>
       <c r="R81" s="21"/>
       <c r="S81" s="21"/>
@@ -11979,47 +12011,39 @@
       <c r="U81" s="21"/>
       <c r="V81" s="21"/>
       <c r="W81" s="21"/>
-      <c r="X81" s="21">
-        <v>1950</v>
-      </c>
-      <c r="Y81" s="21">
-        <v>1956</v>
-      </c>
-      <c r="Z81" s="21">
-        <v>1950</v>
-      </c>
-      <c r="AA81" s="21">
-        <v>1950</v>
-      </c>
+      <c r="X81" s="21"/>
+      <c r="Y81" s="21"/>
+      <c r="Z81" s="21"/>
+      <c r="AA81" s="21"/>
       <c r="AB81" s="21"/>
       <c r="AC81" s="21"/>
       <c r="AD81" s="21" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="AE81" s="21"/>
       <c r="AF81" s="21">
-        <v>332</v>
+        <v>68</v>
       </c>
       <c r="AG81" s="24">
-        <v>18393</v>
+        <v>22134</v>
       </c>
       <c r="AH81" s="24">
-        <v>20801</v>
+        <v>23685</v>
       </c>
       <c r="AI81" s="21">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AJ81" s="21" t="s">
         <v>48</v>
       </c>
       <c r="AK81" s="21" t="s">
-        <v>101</v>
+        <v>275</v>
       </c>
       <c r="AL81" s="21">
-        <v>6.5882350000000001</v>
+        <v>4.2435020000000003</v>
       </c>
       <c r="AM81" s="21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN81" s="21">
         <v>1</v>
@@ -12028,321 +12052,329 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:41" s="6" customFormat="1" ht="34">
-      <c r="A82" s="21">
-        <v>145</v>
-      </c>
-      <c r="B82" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C82" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="D82" s="54">
-        <v>22134</v>
-      </c>
-      <c r="E82" s="54">
-        <v>23685</v>
-      </c>
-      <c r="F82" s="21">
-        <v>1964</v>
-      </c>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I82" s="21" t="s">
+    <row r="82" spans="1:41" ht="34">
+      <c r="A82" s="6">
+        <v>516</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D82" s="55">
+        <v>38590</v>
+      </c>
+      <c r="E82" s="55">
+        <v>43990</v>
+      </c>
+      <c r="F82" s="6">
+        <v>2015</v>
+      </c>
+      <c r="G82" s="6">
+        <v>2015</v>
+      </c>
+      <c r="H82" s="33" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I82" s="6" t="s">
         <v>1023</v>
       </c>
-      <c r="J82" s="22" t="s">
+      <c r="J82" s="7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K82" s="7" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L82" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M82" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="N82" s="7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O82" s="6"/>
+      <c r="P82" s="6">
+        <v>2015</v>
+      </c>
+      <c r="Q82" s="6"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="6"/>
+      <c r="T82" s="6"/>
+      <c r="U82" s="6"/>
+      <c r="V82" s="6"/>
+      <c r="W82" s="6">
+        <v>2010</v>
+      </c>
+      <c r="X82" s="6"/>
+      <c r="Y82" s="6"/>
+      <c r="Z82" s="6"/>
+      <c r="AA82" s="6"/>
+      <c r="AB82" s="6"/>
+      <c r="AC82" s="6"/>
+      <c r="AD82" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE82" s="6"/>
+      <c r="AF82" s="6">
+        <v>108</v>
+      </c>
+      <c r="AG82" s="8">
+        <v>38590</v>
+      </c>
+      <c r="AH82" s="8">
+        <v>43830</v>
+      </c>
+      <c r="AI82" s="6">
+        <v>6</v>
+      </c>
+      <c r="AJ82" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK82" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="AL82" s="6">
+        <v>14.33652</v>
+      </c>
+      <c r="AM82" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN82" s="6">
+        <v>2</v>
+      </c>
+      <c r="AO82" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:41" s="6" customFormat="1" ht="17">
+      <c r="A83" s="6">
+        <v>155</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="D83" s="55">
+        <v>26918</v>
+      </c>
+      <c r="E83" s="55">
+        <v>32943</v>
+      </c>
+      <c r="F83" s="6">
+        <v>1980</v>
+      </c>
+      <c r="G83" s="6">
+        <v>1980</v>
+      </c>
+      <c r="H83" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K82" s="22" t="s">
+      <c r="I83" s="6" t="s">
         <v>1024</v>
       </c>
-      <c r="L82" s="22" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M82" s="22" t="s">
-        <v>1200</v>
-      </c>
-      <c r="N82" s="22" t="s">
-        <v>1221</v>
-      </c>
-      <c r="O82" s="21"/>
-      <c r="P82" s="21">
-        <v>1964</v>
-      </c>
-      <c r="Q82" s="21"/>
-      <c r="R82" s="21"/>
-      <c r="S82" s="21"/>
-      <c r="T82" s="21"/>
-      <c r="U82" s="21"/>
-      <c r="V82" s="21"/>
-      <c r="W82" s="21"/>
-      <c r="X82" s="21"/>
-      <c r="Y82" s="21"/>
-      <c r="Z82" s="21"/>
-      <c r="AA82" s="21"/>
-      <c r="AB82" s="21"/>
-      <c r="AC82" s="21"/>
-      <c r="AD82" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE82" s="21"/>
-      <c r="AF82" s="21">
-        <v>68</v>
-      </c>
-      <c r="AG82" s="24">
-        <v>22134</v>
-      </c>
-      <c r="AH82" s="24">
-        <v>23685</v>
-      </c>
-      <c r="AI82" s="21">
-        <v>-3</v>
-      </c>
-      <c r="AJ82" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK82" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="AL82" s="21">
-        <v>4.2435020000000003</v>
-      </c>
-      <c r="AM82" s="21">
-        <v>4</v>
-      </c>
-      <c r="AN82" s="21">
-        <v>1</v>
-      </c>
-      <c r="AO82" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:41" ht="34">
-      <c r="A83" s="6">
-        <v>516</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>1188</v>
-      </c>
-      <c r="D83" s="55">
-        <v>38590</v>
-      </c>
-      <c r="E83" s="55">
-        <v>43990</v>
-      </c>
-      <c r="F83" s="6">
-        <v>2015</v>
-      </c>
-      <c r="G83" s="6">
-        <v>2015</v>
-      </c>
-      <c r="H83" s="33" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J83" s="7" t="s">
-        <v>1013</v>
+      <c r="J83" s="36" t="s">
+        <v>765</v>
       </c>
       <c r="K83" s="7" t="s">
         <v>1023</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="M83" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N83" s="7" t="s">
-        <v>1209</v>
-      </c>
-      <c r="O83" s="6"/>
+        <v>1205</v>
+      </c>
       <c r="P83" s="6">
-        <v>2015</v>
-      </c>
-      <c r="Q83" s="6"/>
-      <c r="R83" s="6"/>
-      <c r="S83" s="6"/>
-      <c r="T83" s="6"/>
-      <c r="U83" s="6"/>
-      <c r="V83" s="6"/>
-      <c r="W83" s="6">
-        <v>2010</v>
-      </c>
-      <c r="X83" s="6"/>
-      <c r="Y83" s="6"/>
-      <c r="Z83" s="6"/>
-      <c r="AA83" s="6"/>
-      <c r="AB83" s="6"/>
-      <c r="AC83" s="6"/>
+        <v>1980</v>
+      </c>
+      <c r="X83" s="6">
+        <v>1973</v>
+      </c>
+      <c r="Y83" s="6">
+        <v>1989</v>
+      </c>
+      <c r="Z83" s="6">
+        <v>1974</v>
+      </c>
+      <c r="AA83" s="6">
+        <v>1973</v>
+      </c>
       <c r="AD83" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE83" s="6"/>
+        <v>52</v>
+      </c>
       <c r="AF83" s="6">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="AG83" s="8">
-        <v>38590</v>
+        <v>26918</v>
       </c>
       <c r="AH83" s="8">
-        <v>43830</v>
+        <v>32943</v>
       </c>
       <c r="AI83" s="6">
-        <v>6</v>
+        <v>-7</v>
       </c>
       <c r="AJ83" s="6" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AK83" s="6" t="s">
-        <v>730</v>
+        <v>405</v>
       </c>
       <c r="AL83" s="6">
-        <v>14.33652</v>
+        <v>16.484269999999999</v>
       </c>
       <c r="AM83" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AN83" s="6">
         <v>2</v>
       </c>
       <c r="AO83" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A84" s="6">
-        <v>155</v>
+        <v>365</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>403</v>
+        <v>580</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>404</v>
+        <v>691</v>
       </c>
       <c r="D84" s="55">
-        <v>26918</v>
-      </c>
-      <c r="E84" s="55">
-        <v>32943</v>
+        <v>36525</v>
+      </c>
+      <c r="E84" s="55" t="s">
+        <v>1180</v>
       </c>
       <c r="F84" s="6">
-        <v>1980</v>
+        <v>2008</v>
       </c>
       <c r="G84" s="6">
-        <v>1980</v>
+        <v>2012</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>45</v>
+        <v>426</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>1024</v>
-      </c>
-      <c r="J84" s="36" t="s">
-        <v>765</v>
+        <v>1023</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>513</v>
       </c>
       <c r="K84" s="7" t="s">
         <v>1023</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="M84" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N84" s="7" t="s">
-        <v>1205</v>
+        <v>973</v>
       </c>
       <c r="P84" s="6">
-        <v>1980</v>
+        <v>2008</v>
+      </c>
+      <c r="T84" s="6">
+        <v>2004</v>
+      </c>
+      <c r="V84" s="6">
+        <v>2004</v>
+      </c>
+      <c r="W84" s="6">
+        <v>2012</v>
       </c>
       <c r="X84" s="6">
-        <v>1973</v>
+        <v>2000</v>
       </c>
       <c r="Y84" s="6">
-        <v>1989</v>
+        <v>2019</v>
       </c>
       <c r="Z84" s="6">
-        <v>1974</v>
+        <v>2000</v>
       </c>
       <c r="AA84" s="6">
-        <v>1973</v>
+        <v>2000</v>
       </c>
       <c r="AD84" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="AF84" s="6">
-        <v>152</v>
+        <v>810</v>
       </c>
       <c r="AG84" s="8">
-        <v>26918</v>
+        <v>36526</v>
       </c>
       <c r="AH84" s="8">
-        <v>32943</v>
+        <v>43830</v>
       </c>
       <c r="AI84" s="6">
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="AJ84" s="6" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AK84" s="6" t="s">
-        <v>405</v>
+        <v>692</v>
       </c>
       <c r="AL84" s="6">
-        <v>16.484269999999999</v>
+        <v>19.98358</v>
       </c>
       <c r="AM84" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN84" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO84" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:41" s="6" customFormat="1" ht="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A85" s="6">
-        <v>365</v>
+        <v>42</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>580</v>
+        <v>288</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>691</v>
+        <v>1174</v>
       </c>
       <c r="D85" s="55">
-        <v>36525</v>
-      </c>
-      <c r="E85" s="55" t="s">
-        <v>1180</v>
+        <v>11186</v>
+      </c>
+      <c r="E85" s="55">
+        <v>22431</v>
       </c>
       <c r="F85" s="6">
-        <v>2008</v>
+        <v>1952</v>
       </c>
       <c r="G85" s="6">
-        <v>2012</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>426</v>
+        <v>1952</v>
+      </c>
+      <c r="H85" s="33" t="s">
+        <v>1100</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>1023</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="K85" s="7" t="s">
-        <v>1023</v>
+        <v>57</v>
+      </c>
+      <c r="K85" s="42" t="s">
+        <v>1024</v>
       </c>
       <c r="L85" s="7" t="s">
         <v>1196</v>
@@ -12351,254 +12383,260 @@
         <v>1201</v>
       </c>
       <c r="N85" s="7" t="s">
-        <v>973</v>
-      </c>
-      <c r="P85" s="6">
-        <v>2008</v>
-      </c>
-      <c r="T85" s="6">
-        <v>2004</v>
-      </c>
-      <c r="V85" s="6">
-        <v>2004</v>
-      </c>
-      <c r="W85" s="6">
-        <v>2012</v>
-      </c>
-      <c r="X85" s="6">
-        <v>2000</v>
-      </c>
-      <c r="Y85" s="6">
+        <v>1204</v>
+      </c>
+      <c r="O85" s="6"/>
+      <c r="P85" s="6"/>
+      <c r="Q85" s="6"/>
+      <c r="R85" s="6"/>
+      <c r="S85" s="6"/>
+      <c r="T85" s="6"/>
+      <c r="U85" s="6"/>
+      <c r="V85" s="6"/>
+      <c r="W85" s="6"/>
+      <c r="X85" s="6"/>
+      <c r="Y85" s="6"/>
+      <c r="Z85" s="6"/>
+      <c r="AA85" s="6"/>
+      <c r="AB85" s="6"/>
+      <c r="AC85" s="6"/>
+      <c r="AD85" s="6"/>
+      <c r="AE85" s="6"/>
+      <c r="AF85" s="6"/>
+      <c r="AG85" s="8"/>
+      <c r="AH85" s="8"/>
+      <c r="AI85" s="6"/>
+      <c r="AJ85" s="6"/>
+      <c r="AK85" s="6"/>
+      <c r="AL85" s="6"/>
+      <c r="AM85" s="6"/>
+      <c r="AN85" s="6"/>
+      <c r="AO85" s="6"/>
+    </row>
+    <row r="86" spans="1:41" s="6" customFormat="1" ht="17">
+      <c r="A86" s="21">
+        <v>780</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="C86" s="27" t="s">
+        <v>724</v>
+      </c>
+      <c r="D86" s="54">
+        <v>38675</v>
+      </c>
+      <c r="E86" s="54">
+        <v>42013</v>
+      </c>
+      <c r="F86" s="21">
+        <v>2010</v>
+      </c>
+      <c r="G86" s="21"/>
+      <c r="H86" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I86" s="21" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J86" s="22" t="s">
+        <v>765</v>
+      </c>
+      <c r="K86" s="41" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L86" s="22" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M86" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="N86" s="22" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O86" s="21"/>
+      <c r="P86" s="21">
+        <v>2010</v>
+      </c>
+      <c r="Q86" s="21"/>
+      <c r="R86" s="21"/>
+      <c r="S86" s="21"/>
+      <c r="T86" s="21"/>
+      <c r="U86" s="21"/>
+      <c r="V86" s="21"/>
+      <c r="W86" s="21"/>
+      <c r="X86" s="21"/>
+      <c r="Y86" s="21"/>
+      <c r="Z86" s="21"/>
+      <c r="AA86" s="21"/>
+      <c r="AB86" s="21"/>
+      <c r="AC86" s="21"/>
+      <c r="AD86" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE86" s="21"/>
+      <c r="AF86" s="21">
+        <v>144</v>
+      </c>
+      <c r="AG86" s="24">
+        <v>38675</v>
+      </c>
+      <c r="AH86" s="24">
+        <v>42013</v>
+      </c>
+      <c r="AI86" s="21">
+        <v>5</v>
+      </c>
+      <c r="AJ86" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK86" s="21" t="s">
+        <v>725</v>
+      </c>
+      <c r="AL86" s="21">
+        <v>9.132695</v>
+      </c>
+      <c r="AM86" s="21">
+        <v>5</v>
+      </c>
+      <c r="AN86" s="21">
+        <v>1</v>
+      </c>
+      <c r="AO86" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:41" ht="17">
+      <c r="A87" s="6">
+        <v>702</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="D87" s="55">
+        <v>33928</v>
+      </c>
+      <c r="E87" s="55">
+        <v>42735</v>
+      </c>
+      <c r="F87" s="6">
+        <v>1999</v>
+      </c>
+      <c r="G87" s="6">
+        <v>2003</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="K87" s="42" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L87" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M87" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="N87" s="7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O87" s="6">
+        <v>1999</v>
+      </c>
+      <c r="P87" s="6">
+        <v>1999</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>2003</v>
+      </c>
+      <c r="R87" s="6"/>
+      <c r="S87" s="6"/>
+      <c r="T87" s="6"/>
+      <c r="U87" s="6"/>
+      <c r="V87" s="6"/>
+      <c r="W87" s="6"/>
+      <c r="X87" s="6">
+        <v>1992</v>
+      </c>
+      <c r="Y87" s="6">
         <v>2019</v>
       </c>
-      <c r="Z85" s="6">
-        <v>2000</v>
-      </c>
-      <c r="AA85" s="6">
-        <v>2000</v>
-      </c>
-      <c r="AD85" s="6" t="s">
+      <c r="Z87" s="6">
+        <v>1992</v>
+      </c>
+      <c r="AA87" s="6">
+        <v>1992</v>
+      </c>
+      <c r="AB87" s="6"/>
+      <c r="AC87" s="6"/>
+      <c r="AD87" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AF85" s="6">
-        <v>810</v>
-      </c>
-      <c r="AG85" s="8">
-        <v>36526</v>
-      </c>
-      <c r="AH85" s="8">
-        <v>43830</v>
-      </c>
-      <c r="AI85" s="6">
-        <v>6</v>
-      </c>
-      <c r="AJ85" s="6" t="s">
+      <c r="AE87" s="6"/>
+      <c r="AF87" s="6">
+        <v>762</v>
+      </c>
+      <c r="AG87" s="8">
+        <v>33928</v>
+      </c>
+      <c r="AH87" s="8">
+        <v>42735</v>
+      </c>
+      <c r="AI87" s="6">
+        <v>-6</v>
+      </c>
+      <c r="AJ87" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AK85" s="6" t="s">
-        <v>692</v>
-      </c>
-      <c r="AL85" s="6">
-        <v>19.98358</v>
-      </c>
-      <c r="AM85" s="6">
-        <v>4</v>
-      </c>
-      <c r="AN85" s="6">
-        <v>5</v>
-      </c>
-      <c r="AO85" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:41" s="21" customFormat="1" ht="17">
-      <c r="A86" s="6">
-        <v>42</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>1174</v>
-      </c>
-      <c r="D86" s="55">
-        <v>11186</v>
-      </c>
-      <c r="E86" s="55">
-        <v>22431</v>
-      </c>
-      <c r="F86" s="6">
-        <v>1952</v>
-      </c>
-      <c r="G86" s="6">
-        <v>1952</v>
-      </c>
-      <c r="H86" s="33" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="K86" s="42" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L86" s="7" t="s">
-        <v>1196</v>
-      </c>
-      <c r="M86" s="7" t="s">
-        <v>1201</v>
-      </c>
-      <c r="N86" s="7" t="s">
-        <v>1204</v>
-      </c>
-      <c r="O86" s="6"/>
-      <c r="P86" s="6"/>
-      <c r="Q86" s="6"/>
-      <c r="R86" s="6"/>
-      <c r="S86" s="6"/>
-      <c r="T86" s="6"/>
-      <c r="U86" s="6"/>
-      <c r="V86" s="6"/>
-      <c r="W86" s="6"/>
-      <c r="X86" s="6"/>
-      <c r="Y86" s="6"/>
-      <c r="Z86" s="6"/>
-      <c r="AA86" s="6"/>
-      <c r="AB86" s="6"/>
-      <c r="AC86" s="6"/>
-      <c r="AD86" s="6"/>
-      <c r="AE86" s="6"/>
-      <c r="AF86" s="6"/>
-      <c r="AG86" s="8"/>
-      <c r="AH86" s="8"/>
-      <c r="AI86" s="6"/>
-      <c r="AJ86" s="6"/>
-      <c r="AK86" s="6"/>
-      <c r="AL86" s="6"/>
-      <c r="AM86" s="6"/>
-      <c r="AN86" s="6"/>
-      <c r="AO86" s="6"/>
-    </row>
-    <row r="87" spans="1:41" s="6" customFormat="1" ht="17">
-      <c r="A87" s="21">
-        <v>780</v>
-      </c>
-      <c r="B87" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="C87" s="27" t="s">
-        <v>724</v>
-      </c>
-      <c r="D87" s="54">
-        <v>38675</v>
-      </c>
-      <c r="E87" s="54">
-        <v>42013</v>
-      </c>
-      <c r="F87" s="21">
-        <v>2010</v>
-      </c>
-      <c r="G87" s="21"/>
-      <c r="H87" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I87" s="21" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J87" s="22" t="s">
-        <v>765</v>
-      </c>
-      <c r="K87" s="41" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L87" s="22" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M87" s="22" t="s">
-        <v>1200</v>
-      </c>
-      <c r="N87" s="22" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O87" s="21"/>
-      <c r="P87" s="21">
-        <v>2010</v>
-      </c>
-      <c r="Q87" s="21"/>
-      <c r="R87" s="21"/>
-      <c r="S87" s="21"/>
-      <c r="T87" s="21"/>
-      <c r="U87" s="21"/>
-      <c r="V87" s="21"/>
-      <c r="W87" s="21"/>
-      <c r="X87" s="21"/>
-      <c r="Y87" s="21"/>
-      <c r="Z87" s="21"/>
-      <c r="AA87" s="21"/>
-      <c r="AB87" s="21"/>
-      <c r="AC87" s="21"/>
-      <c r="AD87" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE87" s="21"/>
-      <c r="AF87" s="21">
-        <v>144</v>
-      </c>
-      <c r="AG87" s="24">
-        <v>38675</v>
-      </c>
-      <c r="AH87" s="24">
-        <v>42013</v>
-      </c>
-      <c r="AI87" s="21">
-        <v>5</v>
-      </c>
-      <c r="AJ87" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK87" s="21" t="s">
-        <v>725</v>
-      </c>
-      <c r="AL87" s="21">
-        <v>9.132695</v>
-      </c>
-      <c r="AM87" s="21">
-        <v>5</v>
-      </c>
-      <c r="AN87" s="21">
-        <v>1</v>
-      </c>
-      <c r="AO87" s="21">
-        <v>1</v>
+      <c r="AK87" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="AL87" s="6">
+        <v>24.095759999999999</v>
+      </c>
+      <c r="AM87" s="6">
+        <v>7</v>
+      </c>
+      <c r="AN87" s="6">
+        <v>3</v>
+      </c>
+      <c r="AO87" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:41" ht="17">
       <c r="A88" s="6">
-        <v>702</v>
+        <v>640</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>657</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>658</v>
+        <v>174</v>
+      </c>
+      <c r="C88" s="45" t="s">
+        <v>1192</v>
       </c>
       <c r="D88" s="55">
-        <v>33928</v>
-      </c>
-      <c r="E88" s="55">
-        <v>42735</v>
+        <v>37694</v>
+      </c>
+      <c r="E88" s="55" t="s">
+        <v>1180</v>
       </c>
       <c r="F88" s="6">
-        <v>1999</v>
+        <v>2017</v>
       </c>
       <c r="G88" s="6">
-        <v>2003</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>213</v>
+        <v>2017</v>
+      </c>
+      <c r="H88" s="33" t="s">
+        <v>1100</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>1023</v>
@@ -12606,686 +12644,680 @@
       <c r="J88" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="K88" s="42" t="s">
+      <c r="K88" s="7" t="s">
         <v>1023</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>1194</v>
+        <v>1223</v>
       </c>
       <c r="M88" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="N88" s="7" t="s">
-        <v>1209</v>
-      </c>
-      <c r="O88" s="6">
-        <v>1999</v>
-      </c>
-      <c r="P88" s="6">
-        <v>1999</v>
-      </c>
-      <c r="Q88" s="6">
-        <v>2003</v>
-      </c>
+      <c r="N88" s="7"/>
+      <c r="O88" s="6"/>
+      <c r="P88" s="6"/>
+      <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
       <c r="S88" s="6"/>
       <c r="T88" s="6"/>
       <c r="U88" s="6"/>
-      <c r="V88" s="6"/>
-      <c r="W88" s="6"/>
-      <c r="X88" s="6">
-        <v>1992</v>
-      </c>
-      <c r="Y88" s="6">
-        <v>2019</v>
-      </c>
-      <c r="Z88" s="6">
-        <v>1992</v>
-      </c>
-      <c r="AA88" s="6">
-        <v>1992</v>
-      </c>
+      <c r="V88" s="6">
+        <v>2017</v>
+      </c>
+      <c r="W88" s="6">
+        <v>2017</v>
+      </c>
+      <c r="X88" s="6"/>
+      <c r="Y88" s="6"/>
+      <c r="Z88" s="6"/>
+      <c r="AA88" s="6"/>
       <c r="AB88" s="6"/>
       <c r="AC88" s="6"/>
       <c r="AD88" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AE88" s="6"/>
       <c r="AF88" s="6">
-        <v>762</v>
+        <v>792</v>
       </c>
       <c r="AG88" s="8">
-        <v>33928</v>
+        <v>37694</v>
       </c>
       <c r="AH88" s="8">
-        <v>42735</v>
+        <v>43830</v>
       </c>
       <c r="AI88" s="6">
+        <v>7</v>
+      </c>
+      <c r="AJ88" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK88" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="AL88" s="6">
+        <v>16.787960000000002</v>
+      </c>
+      <c r="AM88" s="6">
+        <v>14</v>
+      </c>
+      <c r="AN88" s="6">
+        <v>2</v>
+      </c>
+      <c r="AO88" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:41" s="6" customFormat="1" ht="34">
+      <c r="A89" s="21">
+        <v>100</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C89" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="D89" s="54">
+        <v>19523</v>
+      </c>
+      <c r="E89" s="54">
+        <v>20950</v>
+      </c>
+      <c r="F89" s="21">
+        <v>1956</v>
+      </c>
+      <c r="G89" s="21"/>
+      <c r="H89" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="I89" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J89" s="22" t="s">
+        <v>1235</v>
+      </c>
+      <c r="K89" s="22" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L89" s="22" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M89" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="N89" s="22" t="s">
+        <v>953</v>
+      </c>
+      <c r="O89" s="21"/>
+      <c r="P89" s="21"/>
+      <c r="Q89" s="21"/>
+      <c r="R89" s="21"/>
+      <c r="S89" s="21"/>
+      <c r="T89" s="21"/>
+      <c r="U89" s="21"/>
+      <c r="V89" s="21"/>
+      <c r="W89" s="21"/>
+      <c r="X89" s="21">
+        <v>1953</v>
+      </c>
+      <c r="Y89" s="21">
+        <v>1958</v>
+      </c>
+      <c r="Z89" s="21">
+        <v>1954</v>
+      </c>
+      <c r="AA89" s="21">
+        <v>1953</v>
+      </c>
+      <c r="AB89" s="21"/>
+      <c r="AC89" s="21"/>
+      <c r="AD89" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE89" s="21"/>
+      <c r="AF89" s="21">
+        <v>170</v>
+      </c>
+      <c r="AG89" s="24">
+        <v>19523</v>
+      </c>
+      <c r="AH89" s="24">
+        <v>20950</v>
+      </c>
+      <c r="AI89" s="21">
+        <v>-5</v>
+      </c>
+      <c r="AJ89" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK89" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="AL89" s="21">
+        <v>3.9042409999999999</v>
+      </c>
+      <c r="AM89" s="21">
+        <v>1</v>
+      </c>
+      <c r="AN89" s="21">
+        <v>1</v>
+      </c>
+      <c r="AO89" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:41" s="6" customFormat="1" ht="17">
+      <c r="A90" s="6">
+        <v>678</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="D90" s="55">
+        <v>28688</v>
+      </c>
+      <c r="E90" s="55">
+        <v>40964</v>
+      </c>
+      <c r="F90" s="6">
+        <v>2001</v>
+      </c>
+      <c r="G90" s="6">
+        <v>1978</v>
+      </c>
+      <c r="H90" s="33" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="K90" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L90" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="M90" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="N90" s="7" t="s">
+        <v>952</v>
+      </c>
+      <c r="P90" s="6">
+        <v>2001</v>
+      </c>
+      <c r="X90" s="6">
+        <v>1978</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>2011</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>1978</v>
+      </c>
+      <c r="AA90" s="6">
+        <v>1978</v>
+      </c>
+      <c r="AD90" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF90" s="6">
+        <v>887</v>
+      </c>
+      <c r="AG90" s="8">
+        <v>28688</v>
+      </c>
+      <c r="AH90" s="8">
+        <v>40964</v>
+      </c>
+      <c r="AI90" s="6">
         <v>-6</v>
       </c>
-      <c r="AJ88" s="6" t="s">
+      <c r="AJ90" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AK88" s="6" t="s">
-        <v>660</v>
-      </c>
-      <c r="AL88" s="6">
-        <v>24.095759999999999</v>
-      </c>
-      <c r="AM88" s="6">
-        <v>7</v>
-      </c>
-      <c r="AN88" s="6">
-        <v>3</v>
-      </c>
-      <c r="AO88" s="6">
+      <c r="AK90" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="AL90" s="6">
+        <v>33.586869999999998</v>
+      </c>
+      <c r="AM90" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:41" ht="17">
-      <c r="A89" s="6">
-        <v>640</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C89" s="45" t="s">
-        <v>1192</v>
-      </c>
-      <c r="D89" s="55">
-        <v>37694</v>
-      </c>
-      <c r="E89" s="55" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F89" s="6">
-        <v>2017</v>
-      </c>
-      <c r="G89" s="6">
-        <v>2017</v>
-      </c>
-      <c r="H89" s="33" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J89" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="K89" s="7" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L89" s="7" t="s">
-        <v>1223</v>
-      </c>
-      <c r="M89" s="7" t="s">
-        <v>1201</v>
-      </c>
-      <c r="N89" s="7"/>
-      <c r="O89" s="6"/>
-      <c r="P89" s="6"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="6"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6">
-        <v>2017</v>
-      </c>
-      <c r="W89" s="6">
-        <v>2017</v>
-      </c>
-      <c r="X89" s="6"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="6"/>
-      <c r="AB89" s="6"/>
-      <c r="AC89" s="6"/>
-      <c r="AD89" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE89" s="6"/>
-      <c r="AF89" s="6">
-        <v>792</v>
-      </c>
-      <c r="AG89" s="8">
-        <v>37694</v>
-      </c>
-      <c r="AH89" s="8">
-        <v>43830</v>
-      </c>
-      <c r="AI89" s="6">
-        <v>7</v>
-      </c>
-      <c r="AJ89" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK89" s="6" t="s">
-        <v>750</v>
-      </c>
-      <c r="AL89" s="6">
-        <v>16.787960000000002</v>
-      </c>
-      <c r="AM89" s="6">
-        <v>14</v>
-      </c>
-      <c r="AN89" s="6">
+      <c r="AN90" s="6">
         <v>2</v>
       </c>
-      <c r="AO89" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:41" s="6" customFormat="1" ht="34">
-      <c r="A90" s="21">
-        <v>100</v>
-      </c>
-      <c r="B90" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C90" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="D90" s="54">
-        <v>19523</v>
-      </c>
-      <c r="E90" s="54">
-        <v>20950</v>
-      </c>
-      <c r="F90" s="21">
-        <v>1956</v>
-      </c>
-      <c r="G90" s="21"/>
-      <c r="H90" s="21" t="s">
+      <c r="AO90" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:41" ht="17">
+      <c r="A91" s="6">
+        <v>439</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D91" s="55">
+        <v>24110</v>
+      </c>
+      <c r="E91" s="55">
+        <v>29550</v>
+      </c>
+      <c r="F91" s="6">
+        <v>1974</v>
+      </c>
+      <c r="G91" s="6">
+        <v>1974</v>
+      </c>
+      <c r="H91" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I90" s="21" t="s">
+      <c r="I91" s="6" t="s">
         <v>1024</v>
       </c>
-      <c r="J90" s="22" t="s">
-        <v>1235</v>
-      </c>
-      <c r="K90" s="22" t="s">
+      <c r="J91" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="K91" s="42" t="s">
         <v>1024</v>
       </c>
-      <c r="L90" s="22" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M90" s="22" t="s">
-        <v>1200</v>
-      </c>
-      <c r="N90" s="22" t="s">
-        <v>953</v>
-      </c>
-      <c r="O90" s="21"/>
-      <c r="P90" s="21"/>
-      <c r="Q90" s="21"/>
-      <c r="R90" s="21"/>
-      <c r="S90" s="21"/>
-      <c r="T90" s="21"/>
-      <c r="U90" s="21"/>
-      <c r="V90" s="21"/>
-      <c r="W90" s="21"/>
-      <c r="X90" s="21">
-        <v>1953</v>
-      </c>
-      <c r="Y90" s="21">
-        <v>1958</v>
-      </c>
-      <c r="Z90" s="21">
-        <v>1954</v>
-      </c>
-      <c r="AA90" s="21">
-        <v>1953</v>
-      </c>
-      <c r="AB90" s="21"/>
-      <c r="AC90" s="21"/>
-      <c r="AD90" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE90" s="21"/>
-      <c r="AF90" s="21">
-        <v>170</v>
-      </c>
-      <c r="AG90" s="24">
-        <v>19523</v>
-      </c>
-      <c r="AH90" s="24">
-        <v>20950</v>
-      </c>
-      <c r="AI90" s="21">
-        <v>-5</v>
-      </c>
-      <c r="AJ90" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK90" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="AL90" s="21">
-        <v>3.9042409999999999</v>
-      </c>
-      <c r="AM90" s="21">
-        <v>1</v>
-      </c>
-      <c r="AN90" s="21">
-        <v>1</v>
-      </c>
-      <c r="AO90" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:41" s="6" customFormat="1" ht="17">
-      <c r="A91" s="6">
-        <v>678</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="C91" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="D91" s="55">
-        <v>28688</v>
-      </c>
-      <c r="E91" s="55">
-        <v>40964</v>
-      </c>
-      <c r="F91" s="6">
-        <v>2001</v>
-      </c>
-      <c r="G91" s="6">
-        <v>1978</v>
-      </c>
-      <c r="H91" s="33" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J91" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="K91" s="7" t="s">
-        <v>1024</v>
-      </c>
       <c r="L91" s="7" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="M91" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="N91" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="P91" s="6">
-        <v>2001</v>
-      </c>
-      <c r="X91" s="6">
-        <v>1978</v>
-      </c>
-      <c r="Y91" s="6">
-        <v>2011</v>
-      </c>
-      <c r="Z91" s="6">
-        <v>1978</v>
-      </c>
-      <c r="AA91" s="6">
-        <v>1978</v>
-      </c>
-      <c r="AD91" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF91" s="6">
-        <v>887</v>
-      </c>
-      <c r="AG91" s="8">
-        <v>28688</v>
-      </c>
-      <c r="AH91" s="8">
-        <v>40964</v>
-      </c>
-      <c r="AI91" s="6">
-        <v>-6</v>
-      </c>
-      <c r="AJ91" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK91" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="AL91" s="6">
-        <v>33.586869999999998</v>
-      </c>
-      <c r="AM91" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN91" s="6">
-        <v>2</v>
-      </c>
-      <c r="AO91" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:41" ht="17">
-      <c r="A92" s="6">
-        <v>439</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>1178</v>
-      </c>
-      <c r="D92" s="55">
-        <v>24110</v>
-      </c>
-      <c r="E92" s="55">
-        <v>29550</v>
-      </c>
-      <c r="F92" s="6">
-        <v>1974</v>
-      </c>
-      <c r="G92" s="6">
-        <v>1974</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="I92" s="6" t="s">
+      <c r="N91" s="7"/>
+      <c r="O91" s="6"/>
+      <c r="P91" s="6"/>
+      <c r="Q91" s="6"/>
+      <c r="R91" s="6"/>
+      <c r="S91" s="6"/>
+      <c r="T91" s="6"/>
+      <c r="U91" s="6"/>
+      <c r="V91" s="6"/>
+      <c r="W91" s="6"/>
+      <c r="X91" s="6"/>
+      <c r="Y91" s="6"/>
+      <c r="Z91" s="6"/>
+      <c r="AA91" s="6"/>
+      <c r="AB91" s="6"/>
+      <c r="AC91" s="6"/>
+      <c r="AD91" s="6"/>
+      <c r="AE91" s="6"/>
+      <c r="AF91" s="6"/>
+      <c r="AG91" s="8"/>
+      <c r="AH91" s="8"/>
+      <c r="AI91" s="6"/>
+      <c r="AJ91" s="6"/>
+      <c r="AK91" s="6"/>
+      <c r="AL91" s="6"/>
+      <c r="AM91" s="6"/>
+      <c r="AN91" s="6"/>
+      <c r="AO91" s="6"/>
+    </row>
+    <row r="92" spans="1:41" s="6" customFormat="1" ht="34">
+      <c r="A92" s="21">
+        <v>371</v>
+      </c>
+      <c r="B92" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="C92" s="44" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D92" s="54">
+        <v>39547</v>
+      </c>
+      <c r="E92" s="54">
+        <v>43199</v>
+      </c>
+      <c r="F92" s="21">
+        <v>2018</v>
+      </c>
+      <c r="G92" s="21"/>
+      <c r="H92" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I92" s="21" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J92" s="22" t="s">
+        <v>1235</v>
+      </c>
+      <c r="K92" s="22" t="s">
         <v>1024</v>
       </c>
-      <c r="J92" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="K92" s="42" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L92" s="7" t="s">
-        <v>1198</v>
-      </c>
-      <c r="M92" s="7" t="s">
+      <c r="L92" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M92" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="N92" s="22"/>
+      <c r="O92" s="21"/>
+      <c r="P92" s="21"/>
+      <c r="Q92" s="21"/>
+      <c r="R92" s="21"/>
+      <c r="S92" s="21"/>
+      <c r="T92" s="21"/>
+      <c r="U92" s="21"/>
+      <c r="V92" s="21"/>
+      <c r="W92" s="21"/>
+      <c r="X92" s="21"/>
+      <c r="Y92" s="21"/>
+      <c r="Z92" s="21"/>
+      <c r="AA92" s="21"/>
+      <c r="AB92" s="21"/>
+      <c r="AC92" s="21"/>
+      <c r="AD92" s="21"/>
+      <c r="AE92" s="21"/>
+      <c r="AF92" s="21"/>
+      <c r="AG92" s="21"/>
+      <c r="AH92" s="21"/>
+      <c r="AI92" s="21"/>
+      <c r="AJ92" s="21"/>
+      <c r="AK92" s="21"/>
+      <c r="AL92" s="21"/>
+      <c r="AM92" s="21"/>
+      <c r="AN92" s="21"/>
+      <c r="AO92" s="21"/>
+    </row>
+    <row r="93" spans="1:41" s="6" customFormat="1" ht="51">
+      <c r="A93" s="6">
+        <v>520</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="D93" s="55">
+        <v>25497</v>
+      </c>
+      <c r="E93" s="55">
+        <v>33264</v>
+      </c>
+      <c r="F93" s="6">
+        <v>1979</v>
+      </c>
+      <c r="G93" s="6">
+        <v>1984</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L93" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M93" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="N92" s="7"/>
-      <c r="O92" s="6"/>
-      <c r="P92" s="6"/>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="6"/>
-      <c r="S92" s="6"/>
-      <c r="T92" s="6"/>
-      <c r="U92" s="6"/>
-      <c r="V92" s="6"/>
-      <c r="W92" s="6"/>
-      <c r="X92" s="6"/>
-      <c r="Y92" s="6"/>
-      <c r="Z92" s="6"/>
-      <c r="AA92" s="6"/>
-      <c r="AB92" s="6"/>
-      <c r="AC92" s="6"/>
-      <c r="AD92" s="6"/>
-      <c r="AE92" s="6"/>
-      <c r="AF92" s="6"/>
-      <c r="AG92" s="8"/>
-      <c r="AH92" s="8"/>
-      <c r="AI92" s="6"/>
-      <c r="AJ92" s="6"/>
-      <c r="AK92" s="6"/>
-      <c r="AL92" s="6"/>
-      <c r="AM92" s="6"/>
-      <c r="AN92" s="6"/>
-      <c r="AO92" s="6"/>
-    </row>
-    <row r="93" spans="1:41" s="6" customFormat="1" ht="34">
-      <c r="A93" s="21">
-        <v>371</v>
-      </c>
-      <c r="B93" s="21" t="s">
-        <v>597</v>
-      </c>
-      <c r="C93" s="44" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D93" s="54">
-        <v>39547</v>
-      </c>
-      <c r="E93" s="54">
-        <v>43199</v>
-      </c>
-      <c r="F93" s="21">
-        <v>2018</v>
-      </c>
-      <c r="G93" s="21"/>
-      <c r="H93" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I93" s="21" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J93" s="22" t="s">
-        <v>1235</v>
-      </c>
-      <c r="K93" s="22" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L93" s="22" t="s">
-        <v>1223</v>
-      </c>
-      <c r="M93" s="22" t="s">
-        <v>1200</v>
-      </c>
-      <c r="N93" s="22"/>
-      <c r="O93" s="21"/>
-      <c r="P93" s="21"/>
-      <c r="Q93" s="21"/>
-      <c r="R93" s="21"/>
-      <c r="S93" s="21"/>
-      <c r="T93" s="21"/>
-      <c r="U93" s="21"/>
-      <c r="V93" s="21"/>
-      <c r="W93" s="21"/>
-      <c r="X93" s="21"/>
-      <c r="Y93" s="21"/>
-      <c r="Z93" s="21"/>
-      <c r="AA93" s="21"/>
-      <c r="AB93" s="21"/>
-      <c r="AC93" s="21"/>
-      <c r="AD93" s="21"/>
-      <c r="AE93" s="21"/>
-      <c r="AF93" s="21"/>
-      <c r="AG93" s="21"/>
-      <c r="AH93" s="21"/>
-      <c r="AI93" s="21"/>
-      <c r="AJ93" s="21"/>
-      <c r="AK93" s="21"/>
-      <c r="AL93" s="21"/>
-      <c r="AM93" s="21"/>
-      <c r="AN93" s="21"/>
-      <c r="AO93" s="21"/>
-    </row>
-    <row r="94" spans="1:41" s="6" customFormat="1" ht="51">
+      <c r="N93" s="7" t="s">
+        <v>1008</v>
+      </c>
+      <c r="AG93" s="8"/>
+      <c r="AH93" s="8"/>
+    </row>
+    <row r="94" spans="1:41" s="16" customFormat="1" ht="17">
       <c r="A94" s="6">
-        <v>520</v>
+        <v>93</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>464</v>
+        <v>54</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>465</v>
+        <v>357</v>
       </c>
       <c r="D94" s="55">
-        <v>25497</v>
+        <v>24593</v>
       </c>
       <c r="E94" s="55">
-        <v>33264</v>
+        <v>29053</v>
       </c>
       <c r="F94" s="6">
-        <v>1979</v>
+        <v>1971</v>
       </c>
       <c r="G94" s="6">
-        <v>1984</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>213</v>
+        <v>1972</v>
+      </c>
+      <c r="H94" s="33" t="s">
+        <v>1232</v>
       </c>
       <c r="I94" s="6" t="s">
         <v>1023</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>1236</v>
+        <v>45</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="M94" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N94" s="7" t="s">
-        <v>1008</v>
-      </c>
-      <c r="AG94" s="8"/>
-      <c r="AH94" s="8"/>
-    </row>
-    <row r="95" spans="1:41" s="16" customFormat="1" ht="17">
+        <v>1206</v>
+      </c>
+      <c r="O94" s="6"/>
+      <c r="P94" s="6">
+        <v>1972</v>
+      </c>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6">
+        <v>1971</v>
+      </c>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
+      <c r="V94" s="6"/>
+      <c r="W94" s="6"/>
+      <c r="X94" s="6">
+        <v>1936</v>
+      </c>
+      <c r="Y94" s="6">
+        <v>1979</v>
+      </c>
+      <c r="Z94" s="6">
+        <v>1967</v>
+      </c>
+      <c r="AA94" s="6"/>
+      <c r="AB94" s="6"/>
+      <c r="AC94" s="6"/>
+      <c r="AD94" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE94" s="6"/>
+      <c r="AF94" s="6">
+        <v>558</v>
+      </c>
+      <c r="AG94" s="8">
+        <v>24593</v>
+      </c>
+      <c r="AH94" s="8">
+        <v>29053</v>
+      </c>
+      <c r="AI94" s="6">
+        <v>-8</v>
+      </c>
+      <c r="AJ94" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK94" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="AL94" s="6">
+        <v>12.20246</v>
+      </c>
+      <c r="AM94" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN94" s="6">
+        <v>3</v>
+      </c>
+      <c r="AO94" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:41" ht="17">
       <c r="A95" s="6">
-        <v>93</v>
+        <v>451</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>54</v>
+        <v>369</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="D95" s="55">
-        <v>24593</v>
+        <v>24947</v>
       </c>
       <c r="E95" s="55">
-        <v>29053</v>
+        <v>31379</v>
       </c>
       <c r="F95" s="6">
         <v>1971</v>
       </c>
       <c r="G95" s="6">
-        <v>1972</v>
+        <v>1978</v>
       </c>
       <c r="H95" s="33" t="s">
-        <v>1232</v>
+        <v>1100</v>
       </c>
       <c r="I95" s="6" t="s">
         <v>1023</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>45</v>
+        <v>371</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="M95" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N95" s="7" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O95" s="6"/>
+        <v>980</v>
+      </c>
+      <c r="O95" s="6">
+        <v>1985</v>
+      </c>
       <c r="P95" s="6">
-        <v>1972</v>
+        <v>1978</v>
       </c>
       <c r="Q95" s="6"/>
-      <c r="R95" s="6">
+      <c r="R95" s="6"/>
+      <c r="S95" s="6">
         <v>1971</v>
       </c>
-      <c r="S95" s="6"/>
       <c r="T95" s="6"/>
       <c r="U95" s="6"/>
       <c r="V95" s="6"/>
-      <c r="W95" s="6"/>
-      <c r="X95" s="6">
-        <v>1936</v>
-      </c>
-      <c r="Y95" s="6">
-        <v>1979</v>
-      </c>
-      <c r="Z95" s="6">
-        <v>1967</v>
-      </c>
+      <c r="W95" s="6">
+        <v>1971</v>
+      </c>
+      <c r="X95" s="6"/>
+      <c r="Y95" s="6"/>
+      <c r="Z95" s="6"/>
       <c r="AA95" s="6"/>
       <c r="AB95" s="6"/>
       <c r="AC95" s="6"/>
       <c r="AD95" s="6" t="s">
-        <v>48</v>
+        <v>255</v>
       </c>
       <c r="AE95" s="6"/>
       <c r="AF95" s="6">
-        <v>558</v>
+        <v>694</v>
       </c>
       <c r="AG95" s="8">
-        <v>24593</v>
+        <v>24947</v>
       </c>
       <c r="AH95" s="8">
-        <v>29053</v>
+        <v>31379</v>
       </c>
       <c r="AI95" s="6">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="AJ95" s="6" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="AK95" s="6" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="AL95" s="6">
-        <v>12.20246</v>
+        <v>17.597809999999999</v>
       </c>
       <c r="AM95" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN95" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO95" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:41" ht="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:41" s="21" customFormat="1" ht="34">
       <c r="A96" s="6">
-        <v>451</v>
+        <v>150</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>369</v>
+        <v>70</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>370</v>
+        <v>204</v>
       </c>
       <c r="D96" s="55">
-        <v>24947</v>
+        <v>19916</v>
       </c>
       <c r="E96" s="55">
-        <v>31379</v>
+        <v>32542</v>
       </c>
       <c r="F96" s="6">
-        <v>1971</v>
+        <v>1967</v>
       </c>
       <c r="G96" s="6">
-        <v>1978</v>
-      </c>
-      <c r="H96" s="33" t="s">
-        <v>1100</v>
+        <v>1967</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>371</v>
+        <v>45</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="L96" s="7" t="s">
         <v>1194</v>
@@ -13293,318 +13325,312 @@
       <c r="M96" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="N96" s="7" t="s">
-        <v>980</v>
+      <c r="N96" s="12" t="s">
+        <v>1211</v>
       </c>
       <c r="O96" s="6">
-        <v>1985</v>
+        <v>1973</v>
       </c>
       <c r="P96" s="6">
-        <v>1978</v>
-      </c>
-      <c r="Q96" s="6"/>
+        <v>1967</v>
+      </c>
+      <c r="Q96" s="6">
+        <v>1977</v>
+      </c>
       <c r="R96" s="6"/>
-      <c r="S96" s="6">
-        <v>1971</v>
-      </c>
+      <c r="S96" s="6"/>
       <c r="T96" s="6"/>
-      <c r="U96" s="6"/>
+      <c r="U96" s="6">
+        <v>1959</v>
+      </c>
       <c r="V96" s="6"/>
-      <c r="W96" s="6">
-        <v>1971</v>
-      </c>
-      <c r="X96" s="6"/>
-      <c r="Y96" s="6"/>
-      <c r="Z96" s="6"/>
-      <c r="AA96" s="6"/>
+      <c r="W96" s="6"/>
+      <c r="X96" s="6">
+        <v>1954</v>
+      </c>
+      <c r="Y96" s="6">
+        <v>1993</v>
+      </c>
+      <c r="Z96" s="6">
+        <v>1954</v>
+      </c>
+      <c r="AA96" s="6">
+        <v>1954</v>
+      </c>
       <c r="AB96" s="6"/>
       <c r="AC96" s="6"/>
       <c r="AD96" s="6" t="s">
-        <v>255</v>
+        <v>52</v>
       </c>
       <c r="AE96" s="6"/>
       <c r="AF96" s="6">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="AG96" s="8">
-        <v>24947</v>
+        <v>19916</v>
       </c>
       <c r="AH96" s="8">
-        <v>31379</v>
+        <v>32542</v>
       </c>
       <c r="AI96" s="6">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="AJ96" s="6" t="s">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="AK96" s="6" t="s">
-        <v>372</v>
+        <v>205</v>
       </c>
       <c r="AL96" s="6">
-        <v>17.597809999999999</v>
+        <v>34.544460000000001</v>
       </c>
       <c r="AM96" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN96" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO96" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:41" s="21" customFormat="1" ht="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:41" ht="34">
       <c r="A97" s="6">
-        <v>150</v>
+        <v>850</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="D97" s="55">
-        <v>19916</v>
+        <v>18259</v>
       </c>
       <c r="E97" s="55">
-        <v>32542</v>
+        <v>24178</v>
       </c>
       <c r="F97" s="6">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="G97" s="6">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>45</v>
+        <v>1234</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>45</v>
+        <v>1237</v>
       </c>
       <c r="K97" s="7" t="s">
         <v>1024</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="M97" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="N97" s="12" t="s">
-        <v>1211</v>
-      </c>
-      <c r="O97" s="6">
-        <v>1973</v>
-      </c>
+      <c r="N97" s="7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O97" s="6"/>
       <c r="P97" s="6">
-        <v>1967</v>
-      </c>
-      <c r="Q97" s="6">
-        <v>1977</v>
-      </c>
-      <c r="R97" s="6"/>
+        <v>1963</v>
+      </c>
+      <c r="Q97" s="6"/>
+      <c r="R97" s="6">
+        <v>1959</v>
+      </c>
       <c r="S97" s="6"/>
-      <c r="T97" s="6"/>
-      <c r="U97" s="6">
-        <v>1959</v>
-      </c>
+      <c r="T97" s="6">
+        <v>1957</v>
+      </c>
+      <c r="U97" s="6"/>
       <c r="V97" s="6"/>
-      <c r="W97" s="6"/>
+      <c r="W97" s="6">
+        <v>1957</v>
+      </c>
       <c r="X97" s="6">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="Y97" s="6">
-        <v>1993</v>
+        <v>1966</v>
       </c>
       <c r="Z97" s="6">
-        <v>1954</v>
+        <v>1960</v>
       </c>
       <c r="AA97" s="6">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="AB97" s="6"/>
       <c r="AC97" s="6"/>
       <c r="AD97" s="6" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AE97" s="6"/>
       <c r="AF97" s="6">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="AG97" s="8">
-        <v>19916</v>
+        <v>18259</v>
       </c>
       <c r="AH97" s="8">
-        <v>32542</v>
+        <v>24178</v>
       </c>
       <c r="AI97" s="6">
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="AJ97" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="AK97" s="6" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="AL97" s="6">
-        <v>34.544460000000001</v>
+        <v>16.19425</v>
       </c>
       <c r="AM97" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN97" s="6">
         <v>5</v>
       </c>
-      <c r="AN97" s="6">
-        <v>4</v>
-      </c>
       <c r="AO97" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:41" ht="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A98" s="6">
-        <v>850</v>
+        <v>732</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="D98" s="55">
-        <v>18259</v>
+        <v>17760</v>
       </c>
       <c r="E98" s="55">
-        <v>24178</v>
+        <v>22033</v>
       </c>
       <c r="F98" s="6">
-        <v>1963</v>
+        <v>1952</v>
       </c>
       <c r="G98" s="6">
-        <v>1963</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>1234</v>
+        <v>1954</v>
+      </c>
+      <c r="H98" s="33" t="s">
+        <v>1100</v>
       </c>
       <c r="I98" s="6" t="s">
         <v>1023</v>
       </c>
-      <c r="J98" s="7" t="s">
-        <v>1237</v>
+      <c r="J98" s="36" t="s">
+        <v>1226</v>
       </c>
       <c r="K98" s="7" t="s">
         <v>1024</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="M98" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N98" s="7" t="s">
-        <v>1209</v>
-      </c>
-      <c r="O98" s="6"/>
+        <v>1206</v>
+      </c>
+      <c r="O98" s="6">
+        <v>1956</v>
+      </c>
       <c r="P98" s="6">
-        <v>1963</v>
-      </c>
-      <c r="Q98" s="6"/>
-      <c r="R98" s="6">
-        <v>1959</v>
-      </c>
-      <c r="S98" s="6"/>
-      <c r="T98" s="6">
-        <v>1957</v>
-      </c>
-      <c r="U98" s="6"/>
-      <c r="V98" s="6"/>
-      <c r="W98" s="6">
-        <v>1957</v>
+        <v>1954</v>
       </c>
       <c r="X98" s="6">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Y98" s="6">
-        <v>1966</v>
+        <v>1960</v>
       </c>
       <c r="Z98" s="6">
-        <v>1960</v>
+        <v>1952</v>
       </c>
       <c r="AA98" s="6">
-        <v>1949</v>
-      </c>
-      <c r="AB98" s="6"/>
-      <c r="AC98" s="6"/>
+        <v>1948</v>
+      </c>
       <c r="AD98" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AE98" s="6"/>
       <c r="AF98" s="6">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="AG98" s="8">
-        <v>18259</v>
+        <v>17760</v>
       </c>
       <c r="AH98" s="8">
-        <v>24178</v>
+        <v>22033</v>
       </c>
       <c r="AI98" s="6">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="AJ98" s="6" t="s">
         <v>48</v>
       </c>
       <c r="AK98" s="6" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="AL98" s="6">
-        <v>16.19425</v>
+        <v>11.69083</v>
       </c>
       <c r="AM98" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AN98" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO98" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:41" s="6" customFormat="1" ht="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:41" ht="17">
       <c r="A99" s="6">
-        <v>732</v>
+        <v>411</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>114</v>
+        <v>1138</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>115</v>
+        <v>1139</v>
       </c>
       <c r="D99" s="55">
-        <v>17760</v>
-      </c>
-      <c r="E99" s="55">
-        <v>22033</v>
+        <v>29070</v>
+      </c>
+      <c r="E99" s="55" t="s">
+        <v>1180</v>
       </c>
       <c r="F99" s="6">
-        <v>1952</v>
+        <v>1995</v>
       </c>
       <c r="G99" s="6">
-        <v>1954</v>
-      </c>
-      <c r="H99" s="33" t="s">
-        <v>1100</v>
+        <v>1995</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="I99" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="K99" s="7" t="s">
         <v>1023</v>
-      </c>
-      <c r="J99" s="36" t="s">
-        <v>1226</v>
-      </c>
-      <c r="K99" s="7" t="s">
-        <v>1024</v>
       </c>
       <c r="L99" s="7" t="s">
         <v>1194</v>
@@ -13613,105 +13639,83 @@
         <v>1201</v>
       </c>
       <c r="N99" s="7" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O99" s="6">
-        <v>1956</v>
-      </c>
-      <c r="P99" s="6">
-        <v>1954</v>
-      </c>
-      <c r="X99" s="6">
-        <v>1948</v>
-      </c>
-      <c r="Y99" s="6">
-        <v>1960</v>
-      </c>
-      <c r="Z99" s="6">
-        <v>1952</v>
-      </c>
-      <c r="AA99" s="6">
-        <v>1948</v>
-      </c>
-      <c r="AD99" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF99" s="6">
-        <v>410</v>
-      </c>
-      <c r="AG99" s="8">
-        <v>17760</v>
-      </c>
-      <c r="AH99" s="8">
-        <v>22033</v>
-      </c>
-      <c r="AI99" s="6">
-        <v>-3</v>
-      </c>
-      <c r="AJ99" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK99" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL99" s="6">
-        <v>11.69083</v>
-      </c>
-      <c r="AM99" s="6">
-        <v>4</v>
-      </c>
-      <c r="AN99" s="6">
-        <v>3</v>
-      </c>
-      <c r="AO99" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:41" ht="17">
+        <v>1008</v>
+      </c>
+      <c r="O99" s="6"/>
+      <c r="P99" s="6"/>
+      <c r="Q99" s="6"/>
+      <c r="R99" s="6"/>
+      <c r="S99" s="6"/>
+      <c r="T99" s="6"/>
+      <c r="U99" s="6"/>
+      <c r="V99" s="6"/>
+      <c r="W99" s="6"/>
+      <c r="X99" s="6"/>
+      <c r="Y99" s="6"/>
+      <c r="Z99" s="6"/>
+      <c r="AA99" s="6"/>
+      <c r="AB99" s="6"/>
+      <c r="AC99" s="6"/>
+      <c r="AD99" s="6"/>
+      <c r="AE99" s="6"/>
+      <c r="AF99" s="6"/>
+      <c r="AG99" s="8"/>
+      <c r="AH99" s="8"/>
+      <c r="AI99" s="6"/>
+      <c r="AJ99" s="6"/>
+      <c r="AK99" s="6"/>
+      <c r="AL99" s="6"/>
+      <c r="AM99" s="6"/>
+      <c r="AN99" s="6"/>
+      <c r="AO99" s="6"/>
+    </row>
+    <row r="100" spans="1:41" ht="34">
       <c r="A100" s="6">
+        <v>345</v>
+      </c>
+      <c r="B100" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="B100" s="6" t="s">
-        <v>1138</v>
-      </c>
       <c r="C100" s="11" t="s">
-        <v>1139</v>
+        <v>412</v>
       </c>
       <c r="D100" s="55">
-        <v>29070</v>
-      </c>
-      <c r="E100" s="55" t="s">
-        <v>1180</v>
+        <v>16502</v>
+      </c>
+      <c r="E100" s="55">
+        <v>29345</v>
       </c>
       <c r="F100" s="6">
-        <v>1995</v>
+        <v>1974</v>
       </c>
       <c r="G100" s="6">
-        <v>1995</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>138</v>
+        <v>1974</v>
+      </c>
+      <c r="H100" s="33" t="s">
+        <v>1100</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="K100" s="7" t="s">
         <v>1023</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="M100" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N100" s="7" t="s">
-        <v>1008</v>
+        <v>1212</v>
       </c>
       <c r="O100" s="6"/>
-      <c r="P100" s="6"/>
+      <c r="P100" s="6">
+        <v>1974</v>
+      </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
       <c r="S100" s="6"/>
@@ -13725,65 +13729,87 @@
       <c r="AA100" s="6"/>
       <c r="AB100" s="6"/>
       <c r="AC100" s="6"/>
-      <c r="AD100" s="6"/>
+      <c r="AD100" s="6" t="s">
+        <v>413</v>
+      </c>
       <c r="AE100" s="6"/>
-      <c r="AF100" s="6"/>
-      <c r="AG100" s="8"/>
-      <c r="AH100" s="8"/>
-      <c r="AI100" s="6"/>
-      <c r="AJ100" s="6"/>
-      <c r="AK100" s="6"/>
-      <c r="AL100" s="6"/>
-      <c r="AM100" s="6"/>
-      <c r="AN100" s="6"/>
-      <c r="AO100" s="6"/>
-    </row>
-    <row r="101" spans="1:41" ht="34">
+      <c r="AF100" s="6">
+        <v>890</v>
+      </c>
+      <c r="AG100" s="8">
+        <v>16502</v>
+      </c>
+      <c r="AH100" s="8">
+        <v>29345</v>
+      </c>
+      <c r="AI100" s="6">
+        <v>-7</v>
+      </c>
+      <c r="AJ100" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK100" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="AL100" s="6">
+        <v>35.138170000000002</v>
+      </c>
+      <c r="AM100" s="6">
+        <v>29</v>
+      </c>
+      <c r="AN100" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO100" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A101" s="6">
-        <v>345</v>
+        <v>95</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>411</v>
+        <v>50</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>412</v>
+        <v>325</v>
       </c>
       <c r="D101" s="55">
-        <v>16502</v>
+        <v>25123</v>
       </c>
       <c r="E101" s="55">
-        <v>29345</v>
+        <v>29798</v>
       </c>
       <c r="F101" s="6">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="G101" s="6">
-        <v>1974</v>
-      </c>
-      <c r="H101" s="33" t="s">
-        <v>1100</v>
+        <v>1978</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>82</v>
+        <v>976</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="M101" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N101" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="O101" s="6"/>
       <c r="P101" s="6">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="Q101" s="6"/>
       <c r="R101" s="6"/>
@@ -13792,93 +13818,101 @@
       <c r="U101" s="6"/>
       <c r="V101" s="6"/>
       <c r="W101" s="6"/>
-      <c r="X101" s="6"/>
-      <c r="Y101" s="6"/>
-      <c r="Z101" s="6"/>
-      <c r="AA101" s="6"/>
+      <c r="X101" s="6">
+        <v>1968</v>
+      </c>
+      <c r="Y101" s="6">
+        <v>1982</v>
+      </c>
+      <c r="Z101" s="6">
+        <v>1969</v>
+      </c>
+      <c r="AA101" s="6">
+        <v>1968</v>
+      </c>
       <c r="AB101" s="6"/>
       <c r="AC101" s="6"/>
       <c r="AD101" s="6" t="s">
-        <v>413</v>
+        <v>60</v>
       </c>
       <c r="AE101" s="6"/>
       <c r="AF101" s="6">
-        <v>890</v>
+        <v>591</v>
       </c>
       <c r="AG101" s="8">
-        <v>16502</v>
+        <v>25123</v>
       </c>
       <c r="AH101" s="8">
-        <v>29345</v>
+        <v>29798</v>
       </c>
       <c r="AI101" s="6">
         <v>-7</v>
       </c>
       <c r="AJ101" s="6" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AK101" s="6" t="s">
-        <v>414</v>
+        <v>326</v>
       </c>
       <c r="AL101" s="6">
-        <v>35.138170000000002</v>
+        <v>12.790699999999999</v>
       </c>
       <c r="AM101" s="6">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AN101" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO101" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:41" s="21" customFormat="1" ht="17">
+    <row r="102" spans="1:41" ht="17">
       <c r="A102" s="6">
-        <v>95</v>
+        <v>432</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>50</v>
+        <v>495</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>325</v>
+        <v>496</v>
       </c>
       <c r="D102" s="55">
-        <v>25123</v>
+        <v>25161</v>
       </c>
       <c r="E102" s="55">
-        <v>29798</v>
+        <v>33323</v>
       </c>
       <c r="F102" s="6">
-        <v>1978</v>
+        <v>1985</v>
       </c>
       <c r="G102" s="6">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="I102" s="6" t="s">
         <v>1024</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>976</v>
+        <v>138</v>
       </c>
       <c r="K102" s="7" t="s">
         <v>1024</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="M102" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N102" s="7" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="O102" s="6"/>
       <c r="P102" s="6">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -13891,10 +13925,10 @@
         <v>1968</v>
       </c>
       <c r="Y102" s="6">
-        <v>1982</v>
+        <v>1991</v>
       </c>
       <c r="Z102" s="6">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AA102" s="6">
         <v>1968</v>
@@ -13902,32 +13936,32 @@
       <c r="AB102" s="6"/>
       <c r="AC102" s="6"/>
       <c r="AD102" s="6" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AE102" s="6"/>
       <c r="AF102" s="6">
-        <v>591</v>
+        <v>466</v>
       </c>
       <c r="AG102" s="8">
-        <v>25123</v>
+        <v>25161</v>
       </c>
       <c r="AH102" s="8">
-        <v>29798</v>
+        <v>33323</v>
       </c>
       <c r="AI102" s="6">
         <v>-7</v>
       </c>
       <c r="AJ102" s="6" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AK102" s="6" t="s">
-        <v>326</v>
+        <v>499</v>
       </c>
       <c r="AL102" s="6">
-        <v>12.790699999999999</v>
+        <v>22.331050000000001</v>
       </c>
       <c r="AM102" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AN102" s="6">
         <v>2</v>
@@ -13936,197 +13970,138 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:41" ht="17">
-      <c r="A103" s="6">
-        <v>432</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="D103" s="55">
-        <v>25161</v>
-      </c>
-      <c r="E103" s="55">
-        <v>33323</v>
-      </c>
-      <c r="F103" s="6">
-        <v>1985</v>
-      </c>
-      <c r="G103" s="6">
-        <v>1981</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>1024</v>
-      </c>
-      <c r="J103" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="K103" s="7" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L103" s="7" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M103" s="7" t="s">
+    <row r="103" spans="1:41" s="16" customFormat="1" ht="17">
+      <c r="A103" s="4">
+        <v>2</v>
+      </c>
+      <c r="B103" s="40" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C103" s="47" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D103" s="56">
+        <v>42755</v>
+      </c>
+      <c r="E103" s="56">
+        <v>44216</v>
+      </c>
+      <c r="F103" s="4">
+        <v>2021</v>
+      </c>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="K103" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L103" s="5" t="s">
+        <v>1195</v>
+      </c>
+      <c r="M103" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="N103" s="5"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="4"/>
+      <c r="S103" s="4"/>
+      <c r="T103" s="4"/>
+      <c r="U103" s="4"/>
+      <c r="V103" s="4"/>
+      <c r="W103" s="4"/>
+      <c r="X103" s="4"/>
+      <c r="Y103" s="4"/>
+      <c r="Z103" s="4"/>
+      <c r="AA103" s="4"/>
+      <c r="AB103" s="4"/>
+      <c r="AC103" s="4"/>
+      <c r="AD103" s="4"/>
+      <c r="AE103" s="4"/>
+      <c r="AF103" s="4"/>
+      <c r="AG103" s="4"/>
+      <c r="AH103" s="4"/>
+      <c r="AI103" s="4"/>
+      <c r="AJ103" s="4"/>
+      <c r="AK103" s="4"/>
+      <c r="AL103" s="4"/>
+      <c r="AM103" s="4"/>
+      <c r="AN103" s="4"/>
+      <c r="AO103" s="4"/>
+    </row>
+    <row r="104" spans="1:41" s="6" customFormat="1" ht="17">
+      <c r="A104" s="6">
+        <v>375</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D104" s="55">
+        <v>20515</v>
+      </c>
+      <c r="E104" s="55">
+        <v>29978</v>
+      </c>
+      <c r="F104" s="6">
+        <v>1973</v>
+      </c>
+      <c r="G104" s="6">
+        <v>1973</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J104" s="36" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K104" s="7" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L104" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="M104" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="N103" s="7" t="s">
-        <v>1205</v>
-      </c>
-      <c r="O103" s="6"/>
-      <c r="P103" s="6">
-        <v>1981</v>
-      </c>
-      <c r="Q103" s="6"/>
-      <c r="R103" s="6"/>
-      <c r="S103" s="6"/>
-      <c r="T103" s="6"/>
-      <c r="U103" s="6"/>
-      <c r="V103" s="6"/>
-      <c r="W103" s="6"/>
-      <c r="X103" s="6">
-        <v>1968</v>
-      </c>
-      <c r="Y103" s="6">
-        <v>1991</v>
-      </c>
-      <c r="Z103" s="6">
-        <v>1968</v>
-      </c>
-      <c r="AA103" s="6">
-        <v>1968</v>
-      </c>
-      <c r="AB103" s="6"/>
-      <c r="AC103" s="6"/>
-      <c r="AD103" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE103" s="6"/>
-      <c r="AF103" s="6">
-        <v>466</v>
-      </c>
-      <c r="AG103" s="8">
-        <v>25161</v>
-      </c>
-      <c r="AH103" s="8">
-        <v>33323</v>
-      </c>
-      <c r="AI103" s="6">
-        <v>-7</v>
-      </c>
-      <c r="AJ103" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK103" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="AL103" s="6">
-        <v>22.331050000000001</v>
-      </c>
-      <c r="AM103" s="6">
-        <v>13</v>
-      </c>
-      <c r="AN103" s="6">
-        <v>2</v>
-      </c>
-      <c r="AO103" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:41" s="16" customFormat="1" ht="17">
-      <c r="A104" s="4">
-        <v>2</v>
-      </c>
-      <c r="B104" s="40" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C104" s="47" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D104" s="56">
-        <v>42755</v>
-      </c>
-      <c r="E104" s="56">
-        <v>44216</v>
-      </c>
-      <c r="F104" s="4">
-        <v>2021</v>
-      </c>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J104" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="K104" s="5" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L104" s="5" t="s">
-        <v>1195</v>
-      </c>
-      <c r="M104" s="22" t="s">
-        <v>1200</v>
-      </c>
-      <c r="N104" s="5"/>
-      <c r="O104" s="4"/>
-      <c r="P104" s="4"/>
-      <c r="Q104" s="4"/>
-      <c r="R104" s="4"/>
-      <c r="S104" s="4"/>
-      <c r="T104" s="4"/>
-      <c r="U104" s="4"/>
-      <c r="V104" s="4"/>
-      <c r="W104" s="4"/>
-      <c r="X104" s="4"/>
-      <c r="Y104" s="4"/>
-      <c r="Z104" s="4"/>
-      <c r="AA104" s="4"/>
-      <c r="AB104" s="4"/>
-      <c r="AC104" s="4"/>
-      <c r="AD104" s="4"/>
-      <c r="AE104" s="4"/>
-      <c r="AF104" s="4"/>
-      <c r="AG104" s="4"/>
-      <c r="AH104" s="4"/>
-      <c r="AI104" s="4"/>
-      <c r="AJ104" s="4"/>
-      <c r="AK104" s="4"/>
-      <c r="AL104" s="4"/>
-      <c r="AM104" s="4"/>
-      <c r="AN104" s="4"/>
-      <c r="AO104" s="4"/>
+      <c r="N104" s="12"/>
+      <c r="AG104" s="8"/>
+      <c r="AH104" s="8"/>
     </row>
     <row r="105" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A105" s="6">
-        <v>375</v>
+        <v>100</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>393</v>
+        <v>89</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>1177</v>
+        <v>693</v>
       </c>
       <c r="D105" s="55">
-        <v>20515</v>
+        <v>37476</v>
       </c>
       <c r="E105" s="55">
-        <v>29978</v>
+        <v>40397</v>
       </c>
       <c r="F105" s="6">
-        <v>1973</v>
+        <v>2004</v>
       </c>
       <c r="G105" s="6">
-        <v>1973</v>
+        <v>2005</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>67</v>
@@ -14137,415 +14112,451 @@
       <c r="J105" s="36" t="s">
         <v>1230</v>
       </c>
-      <c r="K105" s="7" t="s">
+      <c r="K105" s="42" t="s">
         <v>1023</v>
       </c>
-      <c r="L105" s="7" t="s">
-        <v>1203</v>
+      <c r="L105" s="36" t="s">
+        <v>1194</v>
       </c>
       <c r="M105" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="N105" s="12"/>
-      <c r="AG105" s="8"/>
-      <c r="AH105" s="8"/>
-    </row>
-    <row r="106" spans="1:41" s="6" customFormat="1" ht="17">
+      <c r="N105" s="7" t="s">
+        <v>973</v>
+      </c>
+      <c r="P105" s="6">
+        <v>2005</v>
+      </c>
+      <c r="AD105" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF105" s="6">
+        <v>170</v>
+      </c>
+      <c r="AG105" s="8">
+        <v>37476</v>
+      </c>
+      <c r="AH105" s="8">
+        <v>40397</v>
+      </c>
+      <c r="AI105" s="6">
+        <v>7</v>
+      </c>
+      <c r="AJ105" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK105" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="AL105" s="6">
+        <v>7.9917920000000002</v>
+      </c>
+      <c r="AM105" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN105" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO105" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:41" s="21" customFormat="1" ht="17">
       <c r="A106" s="6">
-        <v>100</v>
+        <v>404</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>693</v>
+        <v>526</v>
+      </c>
+      <c r="C106" s="45" t="s">
+        <v>527</v>
       </c>
       <c r="D106" s="55">
-        <v>37476</v>
+        <v>29539</v>
       </c>
       <c r="E106" s="55">
-        <v>40397</v>
+        <v>36287</v>
       </c>
       <c r="F106" s="6">
-        <v>2004</v>
+        <v>1988</v>
       </c>
       <c r="G106" s="6">
-        <v>2005</v>
+        <v>1984</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>67</v>
+        <v>138</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J106" s="36" t="s">
-        <v>1230</v>
+        <v>1024</v>
+      </c>
+      <c r="J106" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="K106" s="42" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L106" s="36" t="s">
-        <v>1194</v>
+        <v>1024</v>
+      </c>
+      <c r="L106" s="7" t="s">
+        <v>1198</v>
       </c>
       <c r="M106" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N106" s="7" t="s">
-        <v>973</v>
-      </c>
-      <c r="P106" s="6">
-        <v>2005</v>
-      </c>
+        <v>952</v>
+      </c>
+      <c r="O106" s="6"/>
+      <c r="P106" s="6"/>
+      <c r="Q106" s="6"/>
+      <c r="R106" s="6"/>
+      <c r="S106" s="6"/>
+      <c r="T106" s="6"/>
+      <c r="U106" s="6"/>
+      <c r="V106" s="6"/>
+      <c r="W106" s="6"/>
+      <c r="X106" s="6">
+        <v>1980</v>
+      </c>
+      <c r="Y106" s="6">
+        <v>1999</v>
+      </c>
+      <c r="Z106" s="6">
+        <v>1984</v>
+      </c>
+      <c r="AA106" s="6">
+        <v>1980</v>
+      </c>
+      <c r="AB106" s="6"/>
+      <c r="AC106" s="6"/>
       <c r="AD106" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE106" s="6"/>
+      <c r="AF106" s="6">
+        <v>624</v>
+      </c>
+      <c r="AG106" s="8">
+        <v>29539</v>
+      </c>
+      <c r="AH106" s="8">
+        <v>36287</v>
+      </c>
+      <c r="AI106" s="6">
+        <v>-7</v>
+      </c>
+      <c r="AJ106" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK106" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="AL106" s="6">
+        <v>18.46238</v>
+      </c>
+      <c r="AM106" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN106" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO106" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:41" s="21" customFormat="1" ht="17">
+      <c r="A107" s="21">
+        <v>433</v>
+      </c>
+      <c r="B107" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="C107" s="27" t="s">
+        <v>703</v>
+      </c>
+      <c r="D107" s="54">
+        <v>36618</v>
+      </c>
+      <c r="E107" s="54">
+        <v>41001</v>
+      </c>
+      <c r="F107" s="21">
+        <v>2008</v>
+      </c>
+      <c r="H107" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I107" s="31" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="K107" s="22" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L107" s="22" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M107" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="N107" s="22" t="s">
+        <v>1219</v>
+      </c>
+      <c r="O107" s="21">
+        <v>2012</v>
+      </c>
+      <c r="P107" s="21">
+        <v>2008</v>
+      </c>
+      <c r="V107" s="21">
+        <v>2008</v>
+      </c>
+      <c r="AD107" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="AF106" s="6">
-        <v>170</v>
-      </c>
-      <c r="AG106" s="8">
-        <v>37476</v>
-      </c>
-      <c r="AH106" s="8">
-        <v>40397</v>
-      </c>
-      <c r="AI106" s="6">
-        <v>7</v>
-      </c>
-      <c r="AJ106" s="6" t="s">
+      <c r="AF107" s="21">
+        <v>686</v>
+      </c>
+      <c r="AG107" s="24">
+        <v>36618</v>
+      </c>
+      <c r="AH107" s="24">
+        <v>41001</v>
+      </c>
+      <c r="AI107" s="21">
+        <v>8</v>
+      </c>
+      <c r="AJ107" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="AK106" s="6" t="s">
-        <v>694</v>
-      </c>
-      <c r="AL106" s="6">
-        <v>7.9917920000000002</v>
-      </c>
-      <c r="AM106" s="6">
+      <c r="AK107" s="21" t="s">
+        <v>705</v>
+      </c>
+      <c r="AL107" s="21">
+        <v>11.99179</v>
+      </c>
+      <c r="AM107" s="21">
+        <v>8</v>
+      </c>
+      <c r="AN107" s="21">
         <v>3</v>
       </c>
-      <c r="AN106" s="6">
-        <v>1</v>
-      </c>
-      <c r="AO106" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:41" s="21" customFormat="1" ht="17">
-      <c r="A107" s="6">
-        <v>404</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="C107" s="45" t="s">
-        <v>527</v>
-      </c>
-      <c r="D107" s="55">
-        <v>29539</v>
-      </c>
-      <c r="E107" s="55">
-        <v>36287</v>
-      </c>
-      <c r="F107" s="6">
-        <v>1988</v>
-      </c>
-      <c r="G107" s="6">
-        <v>1984</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="I107" s="6" t="s">
+      <c r="AO107" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:41" s="21" customFormat="1" ht="17">
+      <c r="A108" s="6">
+        <v>450</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D108" s="55">
+        <v>16072</v>
+      </c>
+      <c r="E108" s="55">
+        <v>26137</v>
+      </c>
+      <c r="F108" s="6">
+        <v>1949</v>
+      </c>
+      <c r="G108" s="6">
+        <v>1949</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I108" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J108" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K108" s="7" t="s">
         <v>1024</v>
       </c>
-      <c r="J107" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="K107" s="42" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L107" s="7" t="s">
-        <v>1198</v>
-      </c>
-      <c r="M107" s="7" t="s">
+      <c r="L108" s="20" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M108" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="N107" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="O107" s="6"/>
-      <c r="P107" s="6"/>
-      <c r="Q107" s="6"/>
-      <c r="R107" s="6"/>
-      <c r="S107" s="6"/>
-      <c r="T107" s="6"/>
-      <c r="U107" s="6"/>
-      <c r="V107" s="6"/>
-      <c r="W107" s="6"/>
-      <c r="X107" s="6">
+      <c r="N108" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="O108" s="6">
+        <v>1951</v>
+      </c>
+      <c r="P108" s="6">
+        <v>1949</v>
+      </c>
+      <c r="Q108" s="6"/>
+      <c r="R108" s="6"/>
+      <c r="S108" s="6"/>
+      <c r="T108" s="6"/>
+      <c r="U108" s="6"/>
+      <c r="V108" s="6"/>
+      <c r="W108" s="6"/>
+      <c r="X108" s="6">
+        <v>1944</v>
+      </c>
+      <c r="Y108" s="6">
         <v>1980</v>
       </c>
-      <c r="Y107" s="6">
-        <v>1999</v>
-      </c>
-      <c r="Z107" s="6">
-        <v>1984</v>
-      </c>
-      <c r="AA107" s="6">
-        <v>1980</v>
-      </c>
-      <c r="AB107" s="6"/>
-      <c r="AC107" s="6"/>
-      <c r="AD107" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE107" s="6"/>
-      <c r="AF107" s="6">
-        <v>624</v>
-      </c>
-      <c r="AG107" s="8">
-        <v>29539</v>
-      </c>
-      <c r="AH107" s="8">
-        <v>36287</v>
-      </c>
-      <c r="AI107" s="6">
-        <v>-7</v>
-      </c>
-      <c r="AJ107" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK107" s="6" t="s">
-        <v>528</v>
-      </c>
-      <c r="AL107" s="6">
-        <v>18.46238</v>
-      </c>
-      <c r="AM107" s="6">
-        <v>4</v>
-      </c>
-      <c r="AN107" s="6">
-        <v>1</v>
-      </c>
-      <c r="AO107" s="6">
+      <c r="Z108" s="6">
+        <v>1944</v>
+      </c>
+      <c r="AA108" s="6">
+        <v>1944</v>
+      </c>
+      <c r="AB108" s="6"/>
+      <c r="AC108" s="6"/>
+      <c r="AD108" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE108" s="6"/>
+      <c r="AF108" s="6">
+        <v>430</v>
+      </c>
+      <c r="AG108" s="8">
+        <v>16072</v>
+      </c>
+      <c r="AH108" s="8">
+        <v>26137</v>
+      </c>
+      <c r="AI108" s="6">
+        <v>-6</v>
+      </c>
+      <c r="AJ108" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK108" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL108" s="6">
+        <v>27.53762</v>
+      </c>
+      <c r="AM108" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN108" s="6">
+        <v>3</v>
+      </c>
+      <c r="AO108" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:41" s="21" customFormat="1" ht="17">
-      <c r="A108" s="21">
-        <v>433</v>
-      </c>
-      <c r="B108" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="C108" s="27" t="s">
-        <v>703</v>
-      </c>
-      <c r="D108" s="54">
-        <v>36618</v>
-      </c>
-      <c r="E108" s="54">
-        <v>41001</v>
-      </c>
-      <c r="F108" s="21">
-        <v>2008</v>
-      </c>
-      <c r="H108" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I108" s="31" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J108" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="K108" s="22" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L108" s="22" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M108" s="22" t="s">
-        <v>1200</v>
-      </c>
-      <c r="N108" s="22" t="s">
-        <v>1219</v>
-      </c>
-      <c r="O108" s="21">
-        <v>2012</v>
-      </c>
-      <c r="P108" s="21">
-        <v>2008</v>
-      </c>
-      <c r="V108" s="21">
-        <v>2008</v>
-      </c>
-      <c r="AD108" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF108" s="21">
-        <v>686</v>
-      </c>
-      <c r="AG108" s="24">
-        <v>36618</v>
-      </c>
-      <c r="AH108" s="24">
-        <v>41001</v>
-      </c>
-      <c r="AI108" s="21">
-        <v>8</v>
-      </c>
-      <c r="AJ108" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK108" s="21" t="s">
-        <v>705</v>
-      </c>
-      <c r="AL108" s="21">
-        <v>11.99179</v>
-      </c>
-      <c r="AM108" s="21">
-        <v>8</v>
-      </c>
-      <c r="AN108" s="21">
-        <v>3</v>
-      </c>
-      <c r="AO108" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:41" s="21" customFormat="1" ht="17">
+    <row r="109" spans="1:41" s="6" customFormat="1" ht="17">
       <c r="A109" s="6">
-        <v>450</v>
+        <v>710</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>80</v>
+        <v>755</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>81</v>
+        <v>756</v>
       </c>
       <c r="D109" s="55">
-        <v>16072</v>
-      </c>
-      <c r="E109" s="55">
-        <v>26137</v>
+        <v>41228</v>
+      </c>
+      <c r="E109" s="55" t="s">
+        <v>1180</v>
       </c>
       <c r="F109" s="6">
-        <v>1949</v>
+        <v>2018</v>
       </c>
       <c r="G109" s="6">
-        <v>1949</v>
+        <v>2022</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>67</v>
+        <v>665</v>
       </c>
       <c r="I109" s="6" t="s">
         <v>1023</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L109" s="20" t="s">
-        <v>1194</v>
+        <v>1023</v>
+      </c>
+      <c r="L109" s="36" t="s">
+        <v>1202</v>
       </c>
       <c r="M109" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N109" s="7" t="s">
-        <v>1205</v>
-      </c>
-      <c r="O109" s="6">
-        <v>1951</v>
+        <v>973</v>
       </c>
       <c r="P109" s="6">
-        <v>1949</v>
-      </c>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="6"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-      <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6"/>
-      <c r="X109" s="6">
-        <v>1944</v>
-      </c>
-      <c r="Y109" s="6">
-        <v>1980</v>
-      </c>
-      <c r="Z109" s="6">
-        <v>1944</v>
-      </c>
-      <c r="AA109" s="6">
-        <v>1944</v>
-      </c>
-      <c r="AB109" s="6"/>
-      <c r="AC109" s="6"/>
+        <v>2018</v>
+      </c>
       <c r="AD109" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE109" s="6"/>
+        <v>47</v>
+      </c>
       <c r="AF109" s="6">
-        <v>430</v>
+        <v>156</v>
       </c>
       <c r="AG109" s="8">
-        <v>16072</v>
+        <v>41228</v>
       </c>
       <c r="AH109" s="8">
-        <v>26137</v>
+        <v>43830</v>
       </c>
       <c r="AI109" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="AJ109" s="6" t="s">
         <v>48</v>
       </c>
       <c r="AK109" s="6" t="s">
-        <v>83</v>
+        <v>757</v>
       </c>
       <c r="AL109" s="6">
-        <v>27.53762</v>
+        <v>7.1190150000000001</v>
       </c>
       <c r="AM109" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN109" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO109" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:41" s="6" customFormat="1" ht="17">
+    <row r="110" spans="1:41" s="21" customFormat="1" ht="71" customHeight="1">
       <c r="A110" s="6">
-        <v>710</v>
+        <v>500</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>755</v>
+        <v>285</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>756</v>
+        <v>1186</v>
       </c>
       <c r="D110" s="55">
-        <v>41228</v>
+        <v>31441</v>
       </c>
       <c r="E110" s="55" t="s">
         <v>1180</v>
       </c>
       <c r="F110" s="6">
-        <v>2018</v>
+        <v>2005</v>
       </c>
       <c r="G110" s="6">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>665</v>
+        <v>1224</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="J110" s="7" t="s">
         <v>513</v>
@@ -14553,26 +14564,53 @@
       <c r="K110" s="7" t="s">
         <v>1023</v>
       </c>
-      <c r="L110" s="36" t="s">
-        <v>1202</v>
+      <c r="L110" s="7" t="s">
+        <v>1194</v>
       </c>
       <c r="M110" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="N110" s="7" t="s">
-        <v>973</v>
+        <v>1210</v>
+      </c>
+      <c r="O110" s="6">
+        <v>2006</v>
       </c>
       <c r="P110" s="6">
-        <v>2018</v>
-      </c>
+        <v>2005</v>
+      </c>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="6"/>
+      <c r="T110" s="6"/>
+      <c r="U110" s="6"/>
+      <c r="V110" s="6">
+        <v>1991</v>
+      </c>
+      <c r="W110" s="6"/>
+      <c r="X110" s="6">
+        <v>1986</v>
+      </c>
+      <c r="Y110" s="6">
+        <v>2019</v>
+      </c>
+      <c r="Z110" s="6">
+        <v>1986</v>
+      </c>
+      <c r="AA110" s="6">
+        <v>1986</v>
+      </c>
+      <c r="AB110" s="6"/>
+      <c r="AC110" s="6"/>
       <c r="AD110" s="6" t="s">
-        <v>47</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="AE110" s="6"/>
       <c r="AF110" s="6">
-        <v>156</v>
+        <v>800</v>
       </c>
       <c r="AG110" s="8">
-        <v>41228</v>
+        <v>31441</v>
       </c>
       <c r="AH110" s="8">
         <v>43830</v>
@@ -14584,136 +14622,29 @@
         <v>48</v>
       </c>
       <c r="AK110" s="6" t="s">
-        <v>757</v>
+        <v>536</v>
       </c>
       <c r="AL110" s="6">
-        <v>7.1190150000000001</v>
+        <v>33.896030000000003</v>
       </c>
       <c r="AM110" s="6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN110" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO110" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:41" s="21" customFormat="1" ht="71" customHeight="1">
-      <c r="A111" s="6">
-        <v>500</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C111" s="11" t="s">
-        <v>1186</v>
-      </c>
-      <c r="D111" s="55">
-        <v>31441</v>
-      </c>
-      <c r="E111" s="55" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F111" s="6">
-        <v>2005</v>
-      </c>
-      <c r="G111" s="6">
-        <v>1986</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I111" s="6" t="s">
-        <v>1024</v>
-      </c>
-      <c r="J111" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="K111" s="7" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L111" s="7" t="s">
-        <v>1194</v>
-      </c>
-      <c r="M111" s="7" t="s">
-        <v>1201</v>
-      </c>
-      <c r="N111" s="7" t="s">
-        <v>1210</v>
-      </c>
-      <c r="O111" s="6">
-        <v>2006</v>
-      </c>
-      <c r="P111" s="6">
-        <v>2005</v>
-      </c>
-      <c r="Q111" s="6"/>
-      <c r="R111" s="6"/>
-      <c r="S111" s="6"/>
-      <c r="T111" s="6"/>
-      <c r="U111" s="6"/>
-      <c r="V111" s="6">
-        <v>1991</v>
-      </c>
-      <c r="W111" s="6"/>
-      <c r="X111" s="6">
-        <v>1986</v>
-      </c>
-      <c r="Y111" s="6">
-        <v>2019</v>
-      </c>
-      <c r="Z111" s="6">
-        <v>1986</v>
-      </c>
-      <c r="AA111" s="6">
-        <v>1986</v>
-      </c>
-      <c r="AB111" s="6"/>
-      <c r="AC111" s="6"/>
-      <c r="AD111" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6">
-        <v>800</v>
-      </c>
-      <c r="AG111" s="8">
-        <v>31441</v>
-      </c>
-      <c r="AH111" s="8">
-        <v>43830</v>
-      </c>
-      <c r="AI111" s="6">
-        <v>-7</v>
-      </c>
-      <c r="AJ111" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK111" s="6" t="s">
-        <v>536</v>
-      </c>
-      <c r="AL111" s="6">
-        <v>33.896030000000003</v>
-      </c>
-      <c r="AM111" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN111" s="6">
-        <v>4</v>
-      </c>
-      <c r="AO111" s="6">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AO111" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AO111">
-      <sortCondition ref="C1:C111"/>
+  <autoFilter ref="A1:AO110" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AO110">
+      <sortCondition ref="C1:C110"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="N81" r:id="rId1" xr:uid="{0BB1CF7B-D4EA-C448-8EC5-05803AB0CC81}"/>
+    <hyperlink ref="N80" r:id="rId1" xr:uid="{0BB1CF7B-D4EA-C448-8EC5-05803AB0CC81}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>

--- a/Autocoup.xlsx
+++ b/Autocoup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qingengdu/GitHub/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23CC09F-E82D-AD47-8C34-D2647DFBB775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FB5660-1674-4140-8FB5-534BE9922511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Autocoup" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3942" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3945" uniqueCount="1230">
   <si>
     <t>ccode</t>
   </si>
@@ -3897,7 +3897,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4061,6 +4061,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9373,8 +9376,8 @@
       <c r="D53" s="55">
         <v>34534</v>
       </c>
-      <c r="E53" s="55">
-        <v>42735</v>
+      <c r="E53" s="55" t="s">
+        <v>1178</v>
       </c>
       <c r="F53" s="6">
         <v>2003</v>
@@ -9499,8 +9502,8 @@
       <c r="D55" s="55">
         <v>36288</v>
       </c>
-      <c r="E55" s="55">
-        <v>42735</v>
+      <c r="E55" s="55" t="s">
+        <v>1178</v>
       </c>
       <c r="F55" s="6">
         <v>2010</v>
@@ -10934,7 +10937,7 @@
         <v>2001</v>
       </c>
       <c r="G74" s="6">
-        <v>1978</v>
+        <v>2001</v>
       </c>
       <c r="H74" s="33" t="s">
         <v>1100</v>
@@ -11124,8 +11127,8 @@
       <c r="D76" s="55">
         <v>33928</v>
       </c>
-      <c r="E76" s="55">
-        <v>42735</v>
+      <c r="E76" s="60" t="s">
+        <v>1178</v>
       </c>
       <c r="F76" s="6">
         <v>1999</v>
